--- a/bofa-capex-cycles/20261015_BofA Exhibit 2 - capex cycles (% of GDP).xlsx
+++ b/bofa-capex-cycles/20261015_BofA Exhibit 2 - capex cycles (% of GDP).xlsx
@@ -8,11 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart points" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annual" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hyperscalers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source rebuild" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First-hand vs PDF" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First-hand detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart points" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annual" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hyperscalers" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hyperscalers first-hand" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,12 +23,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0&quot;×&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="+0.00;-0.00;0.00"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="+0.000;-0.000;0.000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +44,10 @@
     <font>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -81,8 +88,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -921,7 +934,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ChartPoints" displayName="ChartPoints" ref="A1:G202" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FirstHand" displayName="FirstHand" ref="A1:G79" headerRowCount="1">
+  <autoFilter ref="A1:G79"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Series"/>
+    <tableColumn id="2" name="Period"/>
+    <tableColumn id="3" name="PDF vector (% GDP)"/>
+    <tableColumn id="4" name="First-hand (% GDP)"/>
+    <tableColumn id="5" name="Difference (pp)"/>
+    <tableColumn id="6" name="First-hand source"/>
+    <tableColumn id="7" name="|Difference|"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ChartPoints" displayName="ChartPoints" ref="A1:G202" headerRowCount="1">
   <autoFilter ref="A1:G202"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Series"/>
@@ -936,8 +965,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Annual" displayName="Annual" ref="A1:E60" headerRowCount="1">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Annual" displayName="Annual" ref="A1:E60" headerRowCount="1">
   <autoFilter ref="A1:E60"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Year"/>
@@ -950,11 +979,11 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Hyperscalers" displayName="Hyperscalers" ref="A1:E18" headerRowCount="1">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Hyperscalers" displayName="Hyperscalers" ref="A1:E18" headerRowCount="1">
   <autoFilter ref="A1:E18"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="Quarter (chart position)"/>
+    <tableColumn id="1" name="Trailing 4 quarters to"/>
     <tableColumn id="2" name="Position (year)"/>
     <tableColumn id="3" name="Hyperscalers"/>
     <tableColumn id="4" name="Hyperscalers (lease adjusted)"/>
@@ -964,16 +993,19 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourceRebuild" displayName="SourceRebuild" ref="A1:F32" headerRowCount="1">
-  <autoFilter ref="A1:F32"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="Series"/>
-    <tableColumn id="2" name="Year"/>
-    <tableColumn id="3" name="Exhibit (PDF vector)"/>
-    <tableColumn id="4" name="Rebuilt from source (Aug 2026)"/>
-    <tableColumn id="5" name="Difference (pp)"/>
-    <tableColumn id="6" name="Rebuild source"/>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HyperFirstHand" displayName="HyperFirstHand" ref="A1:I24" headerRowCount="1">
+  <autoFilter ref="A1:I24"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="TTM to"/>
+    <tableColumn id="2" name="MSFT"/>
+    <tableColumn id="3" name="GOOGL"/>
+    <tableColumn id="4" name="AMZN"/>
+    <tableColumn id="5" name="META"/>
+    <tableColumn id="6" name="ORCL"/>
+    <tableColumn id="7" name="Capex, 5 names ($bn)"/>
+    <tableColumn id="8" name="BEA GDP, TTM ($bn)"/>
+    <tableColumn id="9" name="% of US GDP"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
@@ -1630,6 +1662,2750 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Every panel rebuilt from the first-hand sources behind the footnote, compared with the PDF vector values</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Panel</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>First-hand definition</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Max |diff| (pp)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Mean |diff| (pp)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Railroads</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D4" s="9">
+        <f>_xlfn.MAXIFS('First-hand detail'!$G$2:$G$79,'First-hand detail'!$A$2:$A$79,"rail")</f>
+        <v/>
+      </c>
+      <c r="E4" s="9">
+        <f>AVERAGEIFS('First-hand detail'!$G$2:$G$79,'First-hand detail'!$A$2:$A$79,"rail")</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>O&amp;G 1970s-80s</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" s="9">
+        <f>_xlfn.MAXIFS('First-hand detail'!$G$2:$G$79,'First-hand detail'!$A$2:$A$79,"og70s")</f>
+        <v/>
+      </c>
+      <c r="E5" s="9">
+        <f>AVERAGEIFS('First-hand detail'!$G$2:$G$79,'First-hand detail'!$A$2:$A$79,"og70s")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>O&amp;G shale</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" s="9">
+        <f>_xlfn.MAXIFS('First-hand detail'!$G$2:$G$79,'First-hand detail'!$A$2:$A$79,"shale")</f>
+        <v/>
+      </c>
+      <c r="E6" s="9">
+        <f>AVERAGEIFS('First-hand detail'!$G$2:$G$79,'First-hand detail'!$A$2:$A$79,"shale")</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Telecoms</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 5130, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" s="9">
+        <f>_xlfn.MAXIFS('First-hand detail'!$G$2:$G$79,'First-hand detail'!$A$2:$A$79,"telecom")</f>
+        <v/>
+      </c>
+      <c r="E7" s="9">
+        <f>AVERAGEIFS('First-hand detail'!$G$2:$G$79,'First-hand detail'!$A$2:$A$79,"telecom")</f>
+        <v/>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Hyperscalers</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" s="9">
+        <f>_xlfn.MAXIFS('First-hand detail'!$G$2:$G$79,'First-hand detail'!$A$2:$A$79,"hyper")</f>
+        <v/>
+      </c>
+      <c r="E8" s="9">
+        <f>AVERAGEIFS('First-hand detail'!$G$2:$G$79,'First-hand detail'!$A$2:$A$79,"hyper")</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Matches (RMSE 0.019pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Hyperscalers (lease adjusted)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Not reproducible from filings: the gap to reported capex is 1-2.5x the finance-lease additions companies tag; finance + principal repayments or operating-lease additions do not fit either. Treat it as BofA's own estimate.</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Not reproducible</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dating convention found in the process: BofA plots every post-1970 point three quarters EARLY. A point drawn at position P</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>is the four quarters ending at P+0.75: the hyperscaler point drawn at mid-2021 is TTM to 2022Q1, the last one (mid-2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>is TTM to 2026Q1. Annual year Y is drawn from Y-0.5 to Y+0.25 for the same reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>O&amp;G is broader than drilling: BEA investment by the oil &amp; gas extraction, support-activities-for-mining and pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>industries, all asset types including intellectual property products. Telecoms is the broadcasting &amp; telecoms industry, all assets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BEA vintage used here: Fixed Assets detailed investment updated 30 Sep 2026 and current NIPA GDP; identical to BofA's for these years.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>PDF vector (% GDP)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>First-hand (% GDP)</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Difference (pp)</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>First-hand source</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>|Difference|</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>1.171</v>
+      </c>
+      <c r="E2" s="11">
+        <f>C2-D2</f>
+        <v/>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G2" s="9">
+        <f>ABS(E2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="E3" s="11">
+        <f>C3-D3</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G3" s="9">
+        <f>ABS(E3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1901</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="E4" s="11">
+        <f>C4-D4</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G4" s="9">
+        <f>ABS(E4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1902</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E5" s="11">
+        <f>C5-D5</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G5" s="9">
+        <f>ABS(E5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>1.069</v>
+      </c>
+      <c r="E6" s="11">
+        <f>C6-D6</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G6" s="9">
+        <f>ABS(E6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1904</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1.254</v>
+      </c>
+      <c r="E7" s="11">
+        <f>C7-D7</f>
+        <v/>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G7" s="9">
+        <f>ABS(E7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>1.491</v>
+      </c>
+      <c r="E8" s="11">
+        <f>C8-D8</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G8" s="9">
+        <f>ABS(E8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>1.798</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1.798</v>
+      </c>
+      <c r="E9" s="11">
+        <f>C9-D9</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G9" s="9">
+        <f>ABS(E9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>2.026</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>2.026</v>
+      </c>
+      <c r="E10" s="11">
+        <f>C10-D10</f>
+        <v/>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G10" s="9">
+        <f>ABS(E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1908</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>2.221</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>2.222</v>
+      </c>
+      <c r="E11" s="11">
+        <f>C11-D11</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G11" s="9">
+        <f>ABS(E11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="E12" s="11">
+        <f>C12-D12</f>
+        <v/>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G12" s="9">
+        <f>ABS(E12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1910</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>2.303</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>2.303</v>
+      </c>
+      <c r="E13" s="11">
+        <f>C13-D13</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G13" s="9">
+        <f>ABS(E13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1911</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>2.117</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>2.118</v>
+      </c>
+      <c r="E14" s="11">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G14" s="9">
+        <f>ABS(E14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>1.998</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>1.998</v>
+      </c>
+      <c r="E15" s="11">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G15" s="9">
+        <f>ABS(E15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1913</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>1.979</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1.979</v>
+      </c>
+      <c r="E16" s="11">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G16" s="9">
+        <f>ABS(E16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1914</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="E17" s="11">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G17" s="9">
+        <f>ABS(E17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E18" s="11">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G18" s="9">
+        <f>ABS(E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1916</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="E19" s="11">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G19" s="9">
+        <f>ABS(E19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="E20" s="11">
+        <f>C20-D20</f>
+        <v/>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G20" s="9">
+        <f>ABS(E20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1918</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="E21" s="11">
+        <f>C21-D21</f>
+        <v/>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G21" s="9">
+        <f>ABS(E21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="E22" s="11">
+        <f>C22-D22</f>
+        <v/>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G22" s="9">
+        <f>ABS(E22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="E23" s="11">
+        <f>C23-D23</f>
+        <v/>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NBER: Ulmer (1960) Table C-1 col.4 / Kuznets &amp; Jenks (1961) R-22 col.1, R-2 col.7 (1929 prices)</t>
+        </is>
+      </c>
+      <c r="G23" s="9">
+        <f>ABS(E23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E24" s="11">
+        <f>C24-D24</f>
+        <v/>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G24" s="9">
+        <f>ABS(E24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="E25" s="11">
+        <f>C25-D25</f>
+        <v/>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G25" s="9">
+        <f>ABS(E25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="E26" s="11">
+        <f>C26-D26</f>
+        <v/>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G26" s="9">
+        <f>ABS(E26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E27" s="11">
+        <f>C27-D27</f>
+        <v/>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G27" s="9">
+        <f>ABS(E27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="E28" s="11">
+        <f>C28-D28</f>
+        <v/>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G28" s="9">
+        <f>ABS(E28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E29" s="11">
+        <f>C29-D29</f>
+        <v/>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G29" s="9">
+        <f>ABS(E29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E30" s="11">
+        <f>C30-D30</f>
+        <v/>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G30" s="9">
+        <f>ABS(E30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="E31" s="11">
+        <f>C31-D31</f>
+        <v/>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G31" s="9">
+        <f>ABS(E31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="E32" s="11">
+        <f>C32-D32</f>
+        <v/>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G32" s="9">
+        <f>ABS(E32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>1.972</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>1.973</v>
+      </c>
+      <c r="E33" s="11">
+        <f>C33-D33</f>
+        <v/>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G33" s="9">
+        <f>ABS(E33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>1.891</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E34" s="11">
+        <f>C34-D34</f>
+        <v/>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G34" s="9">
+        <f>ABS(E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>1.183</v>
+      </c>
+      <c r="E35" s="11">
+        <f>C35-D35</f>
+        <v/>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G35" s="9">
+        <f>ABS(E35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>1.093</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="E36" s="11">
+        <f>C36-D36</f>
+        <v/>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G36" s="9">
+        <f>ABS(E36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E37" s="11">
+        <f>C37-D37</f>
+        <v/>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G37" s="9">
+        <f>ABS(E37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>og70s</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="E38" s="11">
+        <f>C38-D38</f>
+        <v/>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G38" s="9">
+        <f>ABS(E38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="E39" s="11">
+        <f>C39-D39</f>
+        <v/>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G39" s="9">
+        <f>ABS(E39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="E40" s="11">
+        <f>C40-D40</f>
+        <v/>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G40" s="9">
+        <f>ABS(E40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E41" s="11">
+        <f>C41-D41</f>
+        <v/>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G41" s="9">
+        <f>ABS(E41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="E42" s="11">
+        <f>C42-D42</f>
+        <v/>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G42" s="9">
+        <f>ABS(E42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="E43" s="11">
+        <f>C43-D43</f>
+        <v/>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G43" s="9">
+        <f>ABS(E43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="E44" s="11">
+        <f>C44-D44</f>
+        <v/>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G44" s="9">
+        <f>ABS(E44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="E45" s="11">
+        <f>C45-D45</f>
+        <v/>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G45" s="9">
+        <f>ABS(E45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="E46" s="11">
+        <f>C46-D46</f>
+        <v/>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G46" s="9">
+        <f>ABS(E46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="E47" s="11">
+        <f>C47-D47</f>
+        <v/>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G47" s="9">
+        <f>ABS(E47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="E48" s="11">
+        <f>C48-D48</f>
+        <v/>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G48" s="9">
+        <f>ABS(E48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>1.259</v>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E49" s="11">
+        <f>C49-D49</f>
+        <v/>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G49" s="9">
+        <f>ABS(E49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E50" s="11">
+        <f>C50-D50</f>
+        <v/>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G50" s="9">
+        <f>ABS(E50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="E51" s="11">
+        <f>C51-D51</f>
+        <v/>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G51" s="9">
+        <f>ABS(E51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E52" s="11">
+        <f>C52-D52</f>
+        <v/>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G52" s="9">
+        <f>ABS(E52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>shale</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="E53" s="11">
+        <f>C53-D53</f>
+        <v/>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 2110+2130+4860, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G53" s="9">
+        <f>ABS(E53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="E54" s="11">
+        <f>C54-D54</f>
+        <v/>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 5130, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G54" s="9">
+        <f>ABS(E54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="E55" s="11">
+        <f>C55-D55</f>
+        <v/>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 5130, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G55" s="9">
+        <f>ABS(E55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>1.098</v>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="E56" s="11">
+        <f>C56-D56</f>
+        <v/>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 5130, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G56" s="9">
+        <f>ABS(E56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>1.136</v>
+      </c>
+      <c r="E57" s="11">
+        <f>C57-D57</f>
+        <v/>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 5130, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G57" s="9">
+        <f>ABS(E57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="E58" s="11">
+        <f>C58-D58</f>
+        <v/>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 5130, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G58" s="9">
+        <f>ABS(E58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>1.541</v>
+      </c>
+      <c r="E59" s="11">
+        <f>C59-D59</f>
+        <v/>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 5130, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G59" s="9">
+        <f>ABS(E59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="E60" s="11">
+        <f>C60-D60</f>
+        <v/>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 5130, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G60" s="9">
+        <f>ABS(E60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="E61" s="11">
+        <f>C61-D61</f>
+        <v/>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 5130, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G61" s="9">
+        <f>ABS(E61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E62" s="11">
+        <f>C62-D62</f>
+        <v/>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets: investment by industry 5130, all assets / GDP</t>
+        </is>
+      </c>
+      <c r="G62" s="9">
+        <f>ABS(E62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>TTM to 2022Q1</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="E63" s="11">
+        <f>C63-D63</f>
+        <v/>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G63" s="9">
+        <f>ABS(E63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>TTM to 2022Q2</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="E64" s="11">
+        <f>C64-D64</f>
+        <v/>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G64" s="9">
+        <f>ABS(E64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>TTM to 2022Q3</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="E65" s="11">
+        <f>C65-D65</f>
+        <v/>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G65" s="9">
+        <f>ABS(E65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>TTM to 2022Q4</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E66" s="11">
+        <f>C66-D66</f>
+        <v/>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G66" s="9">
+        <f>ABS(E66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>TTM to 2023Q1</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="E67" s="11">
+        <f>C67-D67</f>
+        <v/>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G67" s="9">
+        <f>ABS(E67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>TTM to 2023Q2</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="E68" s="11">
+        <f>C68-D68</f>
+        <v/>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G68" s="9">
+        <f>ABS(E68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>TTM to 2023Q3</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="E69" s="11">
+        <f>C69-D69</f>
+        <v/>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G69" s="9">
+        <f>ABS(E69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TTM to 2023Q4</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="E70" s="11">
+        <f>C70-D70</f>
+        <v/>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G70" s="9">
+        <f>ABS(E70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TTM to 2024Q1</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E71" s="11">
+        <f>C71-D71</f>
+        <v/>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G71" s="9">
+        <f>ABS(E71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>TTM to 2024Q2</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="E72" s="11">
+        <f>C72-D72</f>
+        <v/>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G72" s="9">
+        <f>ABS(E72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>TTM to 2024Q3</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="E73" s="11">
+        <f>C73-D73</f>
+        <v/>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G73" s="9">
+        <f>ABS(E73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>TTM to 2024Q4</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="E74" s="11">
+        <f>C74-D74</f>
+        <v/>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G74" s="9">
+        <f>ABS(E74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>TTM to 2025Q1</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="E75" s="11">
+        <f>C75-D75</f>
+        <v/>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G75" s="9">
+        <f>ABS(E75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>TTM to 2025Q2</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>1.039</v>
+      </c>
+      <c r="E76" s="11">
+        <f>C76-D76</f>
+        <v/>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G76" s="9">
+        <f>ABS(E76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>TTM to 2025Q3</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="E77" s="11">
+        <f>C77-D77</f>
+        <v/>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G77" s="9">
+        <f>ABS(E77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TTM to 2025Q4</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="n">
+        <v>1.379</v>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="E78" s="11">
+        <f>C78-D78</f>
+        <v/>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G78" s="9">
+        <f>ABS(E78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>hyper</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TTM to 2026Q1</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>1.536</v>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>1.541</v>
+      </c>
+      <c r="E79" s="11">
+        <f>C79-D79</f>
+        <v/>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>SEC XBRL capex MSFT+GOOGL+AMZN+META+ORCL, TTM / BEA GDP TTM</t>
+        </is>
+      </c>
+      <c r="G79" s="9">
+        <f>ABS(E79)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1672,7 +4448,7 @@
           <t>Year (annual series)</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>Years since start (value)</t>
         </is>
@@ -7212,7 +9988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7741,7 +10517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7760,7 +10536,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Quarter (chart position)</t>
+          <t>Trailing 4 quarters to</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -7787,7 +10563,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2021-Jul</t>
+          <t>TTM to 2022Q1</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -7807,7 +10583,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2021-Oct</t>
+          <t>TTM to 2022Q2</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -7827,7 +10603,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2022-Jan</t>
+          <t>TTM to 2022Q3</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -7847,7 +10623,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2022-Apr</t>
+          <t>TTM to 2022Q4</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -7867,7 +10643,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2022-Jul</t>
+          <t>TTM to 2023Q1</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7887,7 +10663,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2022-Oct</t>
+          <t>TTM to 2023Q2</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7907,7 +10683,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023-Jan</t>
+          <t>TTM to 2023Q3</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7927,7 +10703,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023-Apr</t>
+          <t>TTM to 2023Q4</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7947,7 +10723,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023-Jul</t>
+          <t>TTM to 2024Q1</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7967,7 +10743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023-Oct</t>
+          <t>TTM to 2024Q2</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -7987,7 +10763,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-Jan</t>
+          <t>TTM to 2024Q3</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -8007,7 +10783,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-Apr</t>
+          <t>TTM to 2024Q4</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -8027,7 +10803,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-Jul</t>
+          <t>TTM to 2025Q1</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -8047,7 +10823,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-Oct</t>
+          <t>TTM to 2025Q2</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -8067,7 +10843,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-Jan</t>
+          <t>TTM to 2025Q3</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -8087,7 +10863,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-Apr</t>
+          <t>TTM to 2025Q4</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -8107,7 +10883,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-Jul</t>
+          <t>TTM to 2026Q1</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -8132,827 +10908,836 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Series</t>
+          <t>TTM to</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Exhibit (PDF vector)</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Rebuilt from source (Aug 2026)</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Difference (pp)</t>
+          <t>META</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Rebuild source</t>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Capex, 5 names ($bn)</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>BEA GDP, TTM ($bn)</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>% of US GDP</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1900</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1.247</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E2" s="9">
-        <f>D2-C2</f>
-        <v/>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2020Q4</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G2" s="6">
+        <f>SUM(B2:F2)</f>
+        <v/>
+      </c>
+      <c r="H2" s="13" t="n">
+        <v>21375</v>
+      </c>
+      <c r="I2" s="3">
+        <f>G2/H2*100</f>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1901</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.047</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E3" s="9">
-        <f>D3-C3</f>
-        <v/>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2021Q1</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G3" s="6">
+        <f>SUM(B3:F3)</f>
+        <v/>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>21614</v>
+      </c>
+      <c r="I3" s="3">
+        <f>G3/H3*100</f>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1902</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.068</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E4" s="9">
-        <f>D4-C4</f>
-        <v/>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2021Q2</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G4" s="6">
+        <f>SUM(B4:F4)</f>
+        <v/>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>22488</v>
+      </c>
+      <c r="I4" s="3">
+        <f>G4/H4*100</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1903</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.068</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E5" s="9">
-        <f>D5-C5</f>
-        <v/>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2021Q3</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G5" s="6">
+        <f>SUM(B5:F5)</f>
+        <v/>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>23062</v>
+      </c>
+      <c r="I5" s="3">
+        <f>G5/H5*100</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1904</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1.252</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E6" s="9">
-        <f>D6-C6</f>
-        <v/>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2021Q4</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G6" s="6">
+        <f>SUM(B6:F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>23746</v>
+      </c>
+      <c r="I6" s="3">
+        <f>G6/H6*100</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1905</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="E7" s="9">
-        <f>D7-C7</f>
-        <v/>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2022Q1</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G7" s="6">
+        <f>SUM(B7:F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>24385</v>
+      </c>
+      <c r="I7" s="3">
+        <f>G7/H7*100</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1906</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.798</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E8" s="9">
-        <f>D8-C8</f>
-        <v/>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2022Q2</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>24988</v>
+      </c>
+      <c r="I8" s="3">
+        <f>G8/H8*100</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1907</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.026</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E9" s="9">
-        <f>D9-C9</f>
-        <v/>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2022Q3</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G9" s="6">
+        <f>SUM(B9:F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>25572</v>
+      </c>
+      <c r="I9" s="3">
+        <f>G9/H9*100</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1908</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2.221</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="E10" s="9">
-        <f>D10-C10</f>
-        <v/>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2022Q4</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G10" s="6">
+        <f>SUM(B10:F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>26060</v>
+      </c>
+      <c r="I10" s="3">
+        <f>G10/H10*100</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1909</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.115</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E11" s="9">
-        <f>D11-C11</f>
-        <v/>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2023Q1</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G11" s="6">
+        <f>SUM(B11:F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>26555</v>
+      </c>
+      <c r="I11" s="3">
+        <f>G11/H11*100</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1910</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2.303</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E12" s="9">
-        <f>D12-C12</f>
-        <v/>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2023Q2</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G12" s="6">
+        <f>SUM(B12:F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>26971</v>
+      </c>
+      <c r="I12" s="3">
+        <f>G12/H12*100</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1911</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2.117</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E13" s="9">
-        <f>D13-C13</f>
-        <v/>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2023Q3</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G13" s="6">
+        <f>SUM(B13:F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>27403</v>
+      </c>
+      <c r="I13" s="3">
+        <f>G13/H13*100</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1912</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.998</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="9">
-        <f>D14-C14</f>
-        <v/>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2023Q4</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G14" s="6">
+        <f>SUM(B14:F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>27826</v>
+      </c>
+      <c r="I14" s="3">
+        <f>G14/H14*100</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1913</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.979</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E15" s="9">
-        <f>D15-C15</f>
-        <v/>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" s="6">
+        <f>SUM(B15:F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>28214</v>
+      </c>
+      <c r="I15" s="3">
+        <f>G15/H15*100</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1914</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.418</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E16" s="9">
-        <f>D16-C16</f>
-        <v/>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G16" s="6">
+        <f>SUM(B16:F16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>28639</v>
+      </c>
+      <c r="I16" s="3">
+        <f>G16/H16*100</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1915</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E17" s="9">
-        <f>D17-C17</f>
-        <v/>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G17" s="6">
+        <f>SUM(B17:F17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>29015</v>
+      </c>
+      <c r="I17" s="3">
+        <f>G17/H17*100</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1916</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E18" s="9">
-        <f>D18-C18</f>
-        <v/>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2024Q4</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G18" s="6">
+        <f>SUM(B18:F18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>29381</v>
+      </c>
+      <c r="I18" s="3">
+        <f>G18/H18*100</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1917</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.013</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E19" s="9">
-        <f>D19-C19</f>
-        <v/>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G19" s="6">
+        <f>SUM(B19:F19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>29726</v>
+      </c>
+      <c r="I19" s="3">
+        <f>G19/H19*100</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1918</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E20" s="9">
-        <f>D20-C20</f>
-        <v/>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G20" s="6">
+        <f>SUM(B20:F20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>30075</v>
+      </c>
+      <c r="I20" s="3">
+        <f>G20/H20*100</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1919</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E21" s="9">
-        <f>D21-C21</f>
-        <v/>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="G21" s="6">
+        <f>SUM(B21:F21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>30478</v>
+      </c>
+      <c r="I21" s="3">
+        <f>G21/H21*100</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Railroads</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1920</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E22" s="9">
-        <f>D22-C22</f>
-        <v/>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Ulmer (NBER 1960) Table C-1 col.(4) ÷ Kuznets &amp; Jenks (NBER 1961) R-22 / R-2 GNP Variant I, 1929 prices</t>
-        </is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="G22" s="6">
+        <f>SUM(B22:F22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>30861</v>
+      </c>
+      <c r="I22" s="3">
+        <f>G22/H22*100</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hyperscalers</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E23" s="9">
-        <f>D23-C23</f>
-        <v/>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Calendar-year capex of MSFT+GOOGL+AMZN+META+ORCL (SEC XBRL) ÷ BEA GDP; exhibit value = its mid-year (Y+0.5) quarterly point</t>
-        </is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>151</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="G23" s="6">
+        <f>SUM(B23:F23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>31295</v>
+      </c>
+      <c r="I23" s="3">
+        <f>G23/H23*100</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hyperscalers (LA)</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.616</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E24" s="9">
-        <f>D24-C24</f>
-        <v/>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Calendar-year capex of MSFT+GOOGL+AMZN+META+ORCL (SEC XBRL) ÷ BEA GDP; exhibit value = its mid-year (Y+0.5) quarterly point; LA adds finance-lease ROU additions</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Hyperscalers</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E25" s="9">
-        <f>D25-C25</f>
-        <v/>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Calendar-year capex of MSFT+GOOGL+AMZN+META+ORCL (SEC XBRL) ÷ BEA GDP; exhibit value = its mid-year (Y+0.5) quarterly point</t>
-        </is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>132.4</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="G24" s="6">
+        <f>SUM(B24:F24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>31778</v>
+      </c>
+      <c r="I24" s="3">
+        <f>G24/H24*100</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hyperscalers (LA)</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E26" s="9">
-        <f>D26-C26</f>
-        <v/>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Calendar-year capex of MSFT+GOOGL+AMZN+META+ORCL (SEC XBRL) ÷ BEA GDP; exhibit value = its mid-year (Y+0.5) quarterly point; LA adds finance-lease ROU additions</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Hyperscalers</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E27" s="9">
-        <f>D27-C27</f>
-        <v/>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Calendar-year capex of MSFT+GOOGL+AMZN+META+ORCL (SEC XBRL) ÷ BEA GDP; exhibit value = its mid-year (Y+0.5) quarterly point</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Hyperscalers (LA)</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.596</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E28" s="9">
-        <f>D28-C28</f>
-        <v/>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Calendar-year capex of MSFT+GOOGL+AMZN+META+ORCL (SEC XBRL) ÷ BEA GDP; exhibit value = its mid-year (Y+0.5) quarterly point; LA adds finance-lease ROU additions</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Hyperscalers</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.901</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E29" s="9">
-        <f>D29-C29</f>
-        <v/>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Calendar-year capex of MSFT+GOOGL+AMZN+META+ORCL (SEC XBRL) ÷ BEA GDP; exhibit value = its mid-year (Y+0.5) quarterly point</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Hyperscalers (LA)</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1.013</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E30" s="9">
-        <f>D30-C30</f>
-        <v/>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Calendar-year capex of MSFT+GOOGL+AMZN+META+ORCL (SEC XBRL) ÷ BEA GDP; exhibit value = its mid-year (Y+0.5) quarterly point; LA adds finance-lease ROU additions</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Hyperscalers</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1.536</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E31" s="9">
-        <f>D31-C31</f>
-        <v/>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Calendar-year capex of MSFT+GOOGL+AMZN+META+ORCL (SEC XBRL) ÷ BEA GDP; exhibit value = its mid-year (Y+0.5) quarterly point</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Hyperscalers (LA)</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1.702</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="E32" s="9">
-        <f>D32-C32</f>
-        <v/>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Calendar-year capex of MSFT+GOOGL+AMZN+META+ORCL (SEC XBRL) ÷ BEA GDP; exhibit value = its mid-year (Y+0.5) quarterly point; LA adds finance-lease ROU additions</t>
+          <t>SEC XBRL purchases of property &amp; equipment (Amazon: PaymentsToAcquireProductiveAssets), discrete quarters from YTD filings; Oracle's Aug/Nov/Feb/May quarters go in the calendar quarter they end in; GDP = BEA NIPA A191RC. Runs past the exhibit's last point (TTM to 2026Q1).</t>
         </is>
       </c>
     </row>
@@ -8964,13 +11749,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -9007,35 +11792,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Post-1970 series sit on a quarterly grid. Annual series hold each year's value for four quarterly points (mid-year Y-1 to Q1 of Y);</t>
+          <t>Post-1970 series are plotted three quarters early on a quarterly grid: annual year Y fills positions Y-0.5..Y+0.25, and the</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>the 'Year' column assigns that block to Y, which puts the peaks in the known boom years (O&amp;G 1981, telecoms 2000, shale 2014).</t>
+          <t>hyperscaler point at position P is the four quarters ending P+0.75 (labelled 'TTM to ...').</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hyperscaler lines change every quarter (mid-2021 to mid-2025). Their mid-year points are within 0.07pp of calendar-year capex</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>for MSFT+GOOGL+AMZN+META+ORCL over GDP (Source rebuild sheet). The 'Years since start' charts align each cycle on its first point.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Railroads (1899-1920) are annual and match the NBER rebuild year for year (Source rebuild sheet).</t>
+          <t>First-hand rebuild of every panel: 'First-hand vs PDF' sheet (scripts in bofa-capex-cycles/firsthand/).</t>
         </is>
       </c>
     </row>

--- a/bofa-capex-cycles/20261015_BofA Exhibit 2 - capex cycles (% of GDP).xlsx
+++ b/bofa-capex-cycles/20261015_BofA Exhibit 2 - capex cycles (% of GDP).xlsx
@@ -13,8 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart points" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annual" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hyperscalers" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hyperscalers first-hand" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oracle fiscal quarters" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hyperscalers first-hand" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -101,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -130,9 +131,10 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1110,18 +1112,22 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HyperFirstHand" displayName="HyperFirstHand" ref="A1:I24" headerRowCount="1">
-  <autoFilter ref="A1:I24"/>
-  <tableColumns count="9">
-    <tableColumn id="1" name="TTM to"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HyperQuarterly" displayName="HyperQuarterly" ref="A1:M27" headerRowCount="1">
+  <autoFilter ref="A1:M27"/>
+  <tableColumns count="13">
+    <tableColumn id="1" name="Calendar quarter"/>
     <tableColumn id="2" name="MSFT"/>
     <tableColumn id="3" name="GOOGL"/>
     <tableColumn id="4" name="AMZN"/>
     <tableColumn id="5" name="META"/>
-    <tableColumn id="6" name="ORCL"/>
-    <tableColumn id="7" name="Capex, 5 names ($bn)"/>
-    <tableColumn id="8" name="BEA GDP, TTM ($bn)"/>
-    <tableColumn id="9" name="% of US GDP"/>
+    <tableColumn id="6" name="ORCL (calendarised)"/>
+    <tableColumn id="7" name="Capex, 5 names"/>
+    <tableColumn id="8" name="BEA GDP, SAAR"/>
+    <tableColumn id="9" name="TTM capex"/>
+    <tableColumn id="10" name="TTM GDP"/>
+    <tableColumn id="11" name="TTM capex % of GDP"/>
+    <tableColumn id="12" name="BofA chart (PDF)"/>
+    <tableColumn id="13" name="BofA - first-hand (pp)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
@@ -1967,7 +1973,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Matches (RMSE 0.019pp)</t>
+          <t>Matches (RMSE 0.017pp, Oracle calendarised)</t>
         </is>
       </c>
     </row>
@@ -5246,16 +5252,18 @@
           <t>TTM to 2022Q1</t>
         </is>
       </c>
-      <c r="C63" s="15" t="n">
-        <v>139.5</v>
+      <c r="C63" s="18">
+        <f>'Hyperscalers first-hand'!I10</f>
+        <v/>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E63" s="15" t="n">
-        <v>24385</v>
+      <c r="E63" s="18">
+        <f>'Hyperscalers first-hand'!J10</f>
+        <v/>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -5297,16 +5305,18 @@
           <t>TTM to 2022Q2</t>
         </is>
       </c>
-      <c r="C64" s="15" t="n">
-        <v>146.3</v>
+      <c r="C64" s="18">
+        <f>'Hyperscalers first-hand'!I11</f>
+        <v/>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E64" s="15" t="n">
-        <v>24988</v>
+      <c r="E64" s="18">
+        <f>'Hyperscalers first-hand'!J11</f>
+        <v/>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -5348,16 +5358,18 @@
           <t>TTM to 2022Q3</t>
         </is>
       </c>
-      <c r="C65" s="15" t="n">
-        <v>153.6</v>
+      <c r="C65" s="18">
+        <f>'Hyperscalers first-hand'!I12</f>
+        <v/>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E65" s="15" t="n">
-        <v>25572</v>
+      <c r="E65" s="18">
+        <f>'Hyperscalers first-hand'!J12</f>
+        <v/>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -5399,16 +5411,18 @@
           <t>TTM to 2022Q4</t>
         </is>
       </c>
-      <c r="C66" s="15" t="n">
-        <v>157.8</v>
+      <c r="C66" s="18">
+        <f>'Hyperscalers first-hand'!I13</f>
+        <v/>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E66" s="15" t="n">
-        <v>26060</v>
+      <c r="E66" s="18">
+        <f>'Hyperscalers first-hand'!J13</f>
+        <v/>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -5450,16 +5464,18 @@
           <t>TTM to 2023Q1</t>
         </is>
       </c>
-      <c r="C67" s="15" t="n">
-        <v>157.7</v>
+      <c r="C67" s="18">
+        <f>'Hyperscalers first-hand'!I14</f>
+        <v/>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E67" s="15" t="n">
-        <v>26555</v>
+      <c r="E67" s="18">
+        <f>'Hyperscalers first-hand'!J14</f>
+        <v/>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -5501,16 +5517,18 @@
           <t>TTM to 2023Q2</t>
         </is>
       </c>
-      <c r="C68" s="15" t="n">
-        <v>154.6</v>
+      <c r="C68" s="18">
+        <f>'Hyperscalers first-hand'!I15</f>
+        <v/>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E68" s="15" t="n">
-        <v>26971</v>
+      <c r="E68" s="18">
+        <f>'Hyperscalers first-hand'!J15</f>
+        <v/>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -5552,16 +5570,18 @@
           <t>TTM to 2023Q3</t>
         </is>
       </c>
-      <c r="C69" s="15" t="n">
-        <v>151.8</v>
+      <c r="C69" s="18">
+        <f>'Hyperscalers first-hand'!I16</f>
+        <v/>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E69" s="15" t="n">
-        <v>27403</v>
+      <c r="E69" s="18">
+        <f>'Hyperscalers first-hand'!J16</f>
+        <v/>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -5603,16 +5623,18 @@
           <t>TTM to 2023Q4</t>
         </is>
       </c>
-      <c r="C70" s="15" t="n">
-        <v>154.2</v>
+      <c r="C70" s="18">
+        <f>'Hyperscalers first-hand'!I17</f>
+        <v/>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E70" s="15" t="n">
-        <v>27826</v>
+      <c r="E70" s="18">
+        <f>'Hyperscalers first-hand'!J17</f>
+        <v/>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -5654,16 +5676,18 @@
           <t>TTM to 2024Q1</t>
         </is>
       </c>
-      <c r="C71" s="15" t="n">
-        <v>163.6</v>
+      <c r="C71" s="18">
+        <f>'Hyperscalers first-hand'!I18</f>
+        <v/>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E71" s="15" t="n">
-        <v>28214</v>
+      <c r="E71" s="18">
+        <f>'Hyperscalers first-hand'!J18</f>
+        <v/>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -5705,16 +5729,18 @@
           <t>TTM to 2024Q2</t>
         </is>
       </c>
-      <c r="C72" s="15" t="n">
-        <v>183.9</v>
+      <c r="C72" s="18">
+        <f>'Hyperscalers first-hand'!I19</f>
+        <v/>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E72" s="15" t="n">
-        <v>28639</v>
+      <c r="E72" s="18">
+        <f>'Hyperscalers first-hand'!J19</f>
+        <v/>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -5756,16 +5782,18 @@
           <t>TTM to 2024Q3</t>
         </is>
       </c>
-      <c r="C73" s="15" t="n">
-        <v>206.8</v>
+      <c r="C73" s="18">
+        <f>'Hyperscalers first-hand'!I20</f>
+        <v/>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E73" s="15" t="n">
-        <v>29015</v>
+      <c r="E73" s="18">
+        <f>'Hyperscalers first-hand'!J20</f>
+        <v/>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -5807,16 +5835,18 @@
           <t>TTM to 2024Q4</t>
         </is>
       </c>
-      <c r="C74" s="15" t="n">
-        <v>239.1</v>
+      <c r="C74" s="18">
+        <f>'Hyperscalers first-hand'!I21</f>
+        <v/>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E74" s="15" t="n">
-        <v>29381</v>
+      <c r="E74" s="18">
+        <f>'Hyperscalers first-hand'!J21</f>
+        <v/>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -5858,16 +5888,18 @@
           <t>TTM to 2025Q1</t>
         </is>
       </c>
-      <c r="C75" s="15" t="n">
-        <v>270.9</v>
+      <c r="C75" s="18">
+        <f>'Hyperscalers first-hand'!I22</f>
+        <v/>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E75" s="15" t="n">
-        <v>29726</v>
+      <c r="E75" s="18">
+        <f>'Hyperscalers first-hand'!J22</f>
+        <v/>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -5909,16 +5941,18 @@
           <t>TTM to 2025Q2</t>
         </is>
       </c>
-      <c r="C76" s="15" t="n">
-        <v>312.6</v>
+      <c r="C76" s="18">
+        <f>'Hyperscalers first-hand'!I23</f>
+        <v/>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E76" s="15" t="n">
-        <v>30075</v>
+      <c r="E76" s="18">
+        <f>'Hyperscalers first-hand'!J23</f>
+        <v/>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -5960,16 +5994,18 @@
           <t>TTM to 2025Q3</t>
         </is>
       </c>
-      <c r="C77" s="15" t="n">
-        <v>357.2</v>
+      <c r="C77" s="18">
+        <f>'Hyperscalers first-hand'!I24</f>
+        <v/>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E77" s="15" t="n">
-        <v>30478</v>
+      <c r="E77" s="18">
+        <f>'Hyperscalers first-hand'!J24</f>
+        <v/>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6047,18 @@
           <t>TTM to 2025Q4</t>
         </is>
       </c>
-      <c r="C78" s="15" t="n">
-        <v>411.5</v>
+      <c r="C78" s="18">
+        <f>'Hyperscalers first-hand'!I25</f>
+        <v/>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E78" s="15" t="n">
-        <v>30861</v>
+      <c r="E78" s="18">
+        <f>'Hyperscalers first-hand'!J25</f>
+        <v/>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -6062,16 +6100,18 @@
           <t>TTM to 2026Q1</t>
         </is>
       </c>
-      <c r="C79" s="15" t="n">
-        <v>482.1</v>
+      <c r="C79" s="18">
+        <f>'Hyperscalers first-hand'!I26</f>
+        <v/>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
           <t>$bn, TTM capex of the five (SEC)</t>
         </is>
       </c>
-      <c r="E79" s="15" t="n">
-        <v>31295</v>
+      <c r="E79" s="18">
+        <f>'Hyperscalers first-hand'!J26</f>
+        <v/>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -6177,7 +6217,7 @@
         <f>C2-C2</f>
         <v/>
       </c>
-      <c r="E2" s="18" t="n">
+      <c r="E2" s="19" t="n">
         <v>1.169</v>
       </c>
       <c r="F2" s="2" t="n">
@@ -6202,7 +6242,7 @@
         <f>C3-C2</f>
         <v/>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="19" t="n">
         <v>1.247</v>
       </c>
       <c r="F3" s="2" t="n">
@@ -6227,7 +6267,7 @@
         <f>C4-C2</f>
         <v/>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <v>1.047</v>
       </c>
       <c r="F4" s="2" t="n">
@@ -6252,7 +6292,7 @@
         <f>C5-C2</f>
         <v/>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="19" t="n">
         <v>1.068</v>
       </c>
       <c r="F5" s="2" t="n">
@@ -6277,7 +6317,7 @@
         <f>C6-C2</f>
         <v/>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="19" t="n">
         <v>1.068</v>
       </c>
       <c r="F6" s="2" t="n">
@@ -6302,7 +6342,7 @@
         <f>C7-C2</f>
         <v/>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <v>1.252</v>
       </c>
       <c r="F7" s="2" t="n">
@@ -6327,7 +6367,7 @@
         <f>C8-C2</f>
         <v/>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <v>1.49</v>
       </c>
       <c r="F8" s="2" t="n">
@@ -6352,7 +6392,7 @@
         <f>C9-C2</f>
         <v/>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <v>1.798</v>
       </c>
       <c r="F9" s="2" t="n">
@@ -6377,7 +6417,7 @@
         <f>C10-C2</f>
         <v/>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="19" t="n">
         <v>2.026</v>
       </c>
       <c r="F10" s="2" t="n">
@@ -6402,7 +6442,7 @@
         <f>C11-C2</f>
         <v/>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="19" t="n">
         <v>2.221</v>
       </c>
       <c r="F11" s="2" t="n">
@@ -6427,7 +6467,7 @@
         <f>C12-C2</f>
         <v/>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>2.115</v>
       </c>
       <c r="F12" s="2" t="n">
@@ -6452,7 +6492,7 @@
         <f>C13-C2</f>
         <v/>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>2.303</v>
       </c>
       <c r="F13" s="2" t="n">
@@ -6477,7 +6517,7 @@
         <f>C14-C2</f>
         <v/>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>2.117</v>
       </c>
       <c r="F14" s="2" t="n">
@@ -6502,7 +6542,7 @@
         <f>C15-C2</f>
         <v/>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>1.998</v>
       </c>
       <c r="F15" s="2" t="n">
@@ -6527,7 +6567,7 @@
         <f>C16-C2</f>
         <v/>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="19" t="n">
         <v>1.979</v>
       </c>
       <c r="F16" s="2" t="n">
@@ -6552,7 +6592,7 @@
         <f>C17-C2</f>
         <v/>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="19" t="n">
         <v>1.418</v>
       </c>
       <c r="F17" s="2" t="n">
@@ -6577,7 +6617,7 @@
         <f>C18-C2</f>
         <v/>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="19" t="n">
         <v>0.79</v>
       </c>
       <c r="F18" s="2" t="n">
@@ -6602,7 +6642,7 @@
         <f>C19-C2</f>
         <v/>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="19" t="n">
         <v>0.8159999999999999</v>
       </c>
       <c r="F19" s="2" t="n">
@@ -6627,7 +6667,7 @@
         <f>C20-C2</f>
         <v/>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="19" t="n">
         <v>1.013</v>
       </c>
       <c r="F20" s="2" t="n">
@@ -6652,7 +6692,7 @@
         <f>C21-C2</f>
         <v/>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="19" t="n">
         <v>0.78</v>
       </c>
       <c r="F21" s="2" t="n">
@@ -6677,7 +6717,7 @@
         <f>C22-C2</f>
         <v/>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="19" t="n">
         <v>0.508</v>
       </c>
       <c r="F22" s="2" t="n">
@@ -6702,7 +6742,7 @@
         <f>C23-C2</f>
         <v/>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E23" s="19" t="n">
         <v>0.726</v>
       </c>
       <c r="F23" s="2" t="n">
@@ -6727,7 +6767,7 @@
         <f>C24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="19" t="n">
         <v>0.379</v>
       </c>
       <c r="F24" s="2" t="n">
@@ -6752,7 +6792,7 @@
         <f>C25-C24</f>
         <v/>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="19" t="n">
         <v>0.379</v>
       </c>
       <c r="F25" s="2" t="n">
@@ -6777,7 +6817,7 @@
         <f>C26-C24</f>
         <v/>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="19" t="n">
         <v>0.391</v>
       </c>
       <c r="F26" s="2" t="n">
@@ -6802,7 +6842,7 @@
         <f>C27-C24</f>
         <v/>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="19" t="n">
         <v>0.391</v>
       </c>
       <c r="F27" s="2" t="n">
@@ -6827,7 +6867,7 @@
         <f>C28-C24</f>
         <v/>
       </c>
-      <c r="E28" s="18" t="n">
+      <c r="E28" s="19" t="n">
         <v>0.391</v>
       </c>
       <c r="F28" s="2" t="n">
@@ -6852,7 +6892,7 @@
         <f>C29-C24</f>
         <v/>
       </c>
-      <c r="E29" s="18" t="n">
+      <c r="E29" s="19" t="n">
         <v>0.391</v>
       </c>
       <c r="F29" s="2" t="n">
@@ -6877,7 +6917,7 @@
         <f>C30-C24</f>
         <v/>
       </c>
-      <c r="E30" s="18" t="n">
+      <c r="E30" s="19" t="n">
         <v>0.495</v>
       </c>
       <c r="F30" s="2" t="n">
@@ -6902,7 +6942,7 @@
         <f>C31-C24</f>
         <v/>
       </c>
-      <c r="E31" s="18" t="n">
+      <c r="E31" s="19" t="n">
         <v>0.495</v>
       </c>
       <c r="F31" s="2" t="n">
@@ -6927,7 +6967,7 @@
         <f>C32-C24</f>
         <v/>
       </c>
-      <c r="E32" s="18" t="n">
+      <c r="E32" s="19" t="n">
         <v>0.495</v>
       </c>
       <c r="F32" s="2" t="n">
@@ -6952,7 +6992,7 @@
         <f>C33-C24</f>
         <v/>
       </c>
-      <c r="E33" s="18" t="n">
+      <c r="E33" s="19" t="n">
         <v>0.495</v>
       </c>
       <c r="F33" s="2" t="n">
@@ -6977,7 +7017,7 @@
         <f>C34-C24</f>
         <v/>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E34" s="19" t="n">
         <v>0.665</v>
       </c>
       <c r="F34" s="2" t="n">
@@ -7002,7 +7042,7 @@
         <f>C35-C24</f>
         <v/>
       </c>
-      <c r="E35" s="18" t="n">
+      <c r="E35" s="19" t="n">
         <v>0.665</v>
       </c>
       <c r="F35" s="2" t="n">
@@ -7027,7 +7067,7 @@
         <f>C36-C24</f>
         <v/>
       </c>
-      <c r="E36" s="18" t="n">
+      <c r="E36" s="19" t="n">
         <v>0.665</v>
       </c>
       <c r="F36" s="2" t="n">
@@ -7052,7 +7092,7 @@
         <f>C37-C24</f>
         <v/>
       </c>
-      <c r="E37" s="18" t="n">
+      <c r="E37" s="19" t="n">
         <v>0.665</v>
       </c>
       <c r="F37" s="2" t="n">
@@ -7077,7 +7117,7 @@
         <f>C38-C24</f>
         <v/>
       </c>
-      <c r="E38" s="18" t="n">
+      <c r="E38" s="19" t="n">
         <v>0.7</v>
       </c>
       <c r="F38" s="2" t="n">
@@ -7102,7 +7142,7 @@
         <f>C39-C24</f>
         <v/>
       </c>
-      <c r="E39" s="18" t="n">
+      <c r="E39" s="19" t="n">
         <v>0.7</v>
       </c>
       <c r="F39" s="2" t="n">
@@ -7127,7 +7167,7 @@
         <f>C40-C24</f>
         <v/>
       </c>
-      <c r="E40" s="18" t="n">
+      <c r="E40" s="19" t="n">
         <v>0.7</v>
       </c>
       <c r="F40" s="2" t="n">
@@ -7152,7 +7192,7 @@
         <f>C41-C24</f>
         <v/>
       </c>
-      <c r="E41" s="18" t="n">
+      <c r="E41" s="19" t="n">
         <v>0.7</v>
       </c>
       <c r="F41" s="2" t="n">
@@ -7177,7 +7217,7 @@
         <f>C42-C24</f>
         <v/>
       </c>
-      <c r="E42" s="18" t="n">
+      <c r="E42" s="19" t="n">
         <v>0.722</v>
       </c>
       <c r="F42" s="2" t="n">
@@ -7202,7 +7242,7 @@
         <f>C43-C24</f>
         <v/>
       </c>
-      <c r="E43" s="18" t="n">
+      <c r="E43" s="19" t="n">
         <v>0.722</v>
       </c>
       <c r="F43" s="2" t="n">
@@ -7227,7 +7267,7 @@
         <f>C44-C24</f>
         <v/>
       </c>
-      <c r="E44" s="18" t="n">
+      <c r="E44" s="19" t="n">
         <v>0.722</v>
       </c>
       <c r="F44" s="2" t="n">
@@ -7252,7 +7292,7 @@
         <f>C45-C24</f>
         <v/>
       </c>
-      <c r="E45" s="18" t="n">
+      <c r="E45" s="19" t="n">
         <v>0.722</v>
       </c>
       <c r="F45" s="2" t="n">
@@ -7277,7 +7317,7 @@
         <f>C46-C24</f>
         <v/>
       </c>
-      <c r="E46" s="18" t="n">
+      <c r="E46" s="19" t="n">
         <v>0.909</v>
       </c>
       <c r="F46" s="2" t="n">
@@ -7302,7 +7342,7 @@
         <f>C47-C24</f>
         <v/>
       </c>
-      <c r="E47" s="18" t="n">
+      <c r="E47" s="19" t="n">
         <v>0.909</v>
       </c>
       <c r="F47" s="2" t="n">
@@ -7327,7 +7367,7 @@
         <f>C48-C24</f>
         <v/>
       </c>
-      <c r="E48" s="18" t="n">
+      <c r="E48" s="19" t="n">
         <v>0.909</v>
       </c>
       <c r="F48" s="2" t="n">
@@ -7352,7 +7392,7 @@
         <f>C49-C24</f>
         <v/>
       </c>
-      <c r="E49" s="18" t="n">
+      <c r="E49" s="19" t="n">
         <v>0.909</v>
       </c>
       <c r="F49" s="2" t="n">
@@ -7377,7 +7417,7 @@
         <f>C50-C24</f>
         <v/>
       </c>
-      <c r="E50" s="18" t="n">
+      <c r="E50" s="19" t="n">
         <v>1.064</v>
       </c>
       <c r="F50" s="2" t="n">
@@ -7402,7 +7442,7 @@
         <f>C51-C24</f>
         <v/>
       </c>
-      <c r="E51" s="18" t="n">
+      <c r="E51" s="19" t="n">
         <v>1.064</v>
       </c>
       <c r="F51" s="2" t="n">
@@ -7427,7 +7467,7 @@
         <f>C52-C24</f>
         <v/>
       </c>
-      <c r="E52" s="18" t="n">
+      <c r="E52" s="19" t="n">
         <v>1.064</v>
       </c>
       <c r="F52" s="2" t="n">
@@ -7452,7 +7492,7 @@
         <f>C53-C24</f>
         <v/>
       </c>
-      <c r="E53" s="18" t="n">
+      <c r="E53" s="19" t="n">
         <v>1.064</v>
       </c>
       <c r="F53" s="2" t="n">
@@ -7477,7 +7517,7 @@
         <f>C54-C24</f>
         <v/>
       </c>
-      <c r="E54" s="18" t="n">
+      <c r="E54" s="19" t="n">
         <v>1.425</v>
       </c>
       <c r="F54" s="2" t="n">
@@ -7502,7 +7542,7 @@
         <f>C55-C24</f>
         <v/>
       </c>
-      <c r="E55" s="18" t="n">
+      <c r="E55" s="19" t="n">
         <v>1.425</v>
       </c>
       <c r="F55" s="2" t="n">
@@ -7527,7 +7567,7 @@
         <f>C56-C24</f>
         <v/>
       </c>
-      <c r="E56" s="18" t="n">
+      <c r="E56" s="19" t="n">
         <v>1.425</v>
       </c>
       <c r="F56" s="2" t="n">
@@ -7552,7 +7592,7 @@
         <f>C57-C24</f>
         <v/>
       </c>
-      <c r="E57" s="18" t="n">
+      <c r="E57" s="19" t="n">
         <v>1.425</v>
       </c>
       <c r="F57" s="2" t="n">
@@ -7577,7 +7617,7 @@
         <f>C58-C24</f>
         <v/>
       </c>
-      <c r="E58" s="18" t="n">
+      <c r="E58" s="19" t="n">
         <v>1.972</v>
       </c>
       <c r="F58" s="2" t="n">
@@ -7602,7 +7642,7 @@
         <f>C59-C24</f>
         <v/>
       </c>
-      <c r="E59" s="18" t="n">
+      <c r="E59" s="19" t="n">
         <v>1.972</v>
       </c>
       <c r="F59" s="2" t="n">
@@ -7627,7 +7667,7 @@
         <f>C60-C24</f>
         <v/>
       </c>
-      <c r="E60" s="18" t="n">
+      <c r="E60" s="19" t="n">
         <v>1.972</v>
       </c>
       <c r="F60" s="2" t="n">
@@ -7652,7 +7692,7 @@
         <f>C61-C24</f>
         <v/>
       </c>
-      <c r="E61" s="18" t="n">
+      <c r="E61" s="19" t="n">
         <v>1.972</v>
       </c>
       <c r="F61" s="2" t="n">
@@ -7677,7 +7717,7 @@
         <f>C62-C24</f>
         <v/>
       </c>
-      <c r="E62" s="18" t="n">
+      <c r="E62" s="19" t="n">
         <v>1.891</v>
       </c>
       <c r="F62" s="2" t="n">
@@ -7702,7 +7742,7 @@
         <f>C63-C24</f>
         <v/>
       </c>
-      <c r="E63" s="18" t="n">
+      <c r="E63" s="19" t="n">
         <v>1.891</v>
       </c>
       <c r="F63" s="2" t="n">
@@ -7727,7 +7767,7 @@
         <f>C64-C24</f>
         <v/>
       </c>
-      <c r="E64" s="18" t="n">
+      <c r="E64" s="19" t="n">
         <v>1.891</v>
       </c>
       <c r="F64" s="2" t="n">
@@ -7752,7 +7792,7 @@
         <f>C65-C24</f>
         <v/>
       </c>
-      <c r="E65" s="18" t="n">
+      <c r="E65" s="19" t="n">
         <v>1.891</v>
       </c>
       <c r="F65" s="2" t="n">
@@ -7777,7 +7817,7 @@
         <f>C66-C24</f>
         <v/>
       </c>
-      <c r="E66" s="18" t="n">
+      <c r="E66" s="19" t="n">
         <v>1.182</v>
       </c>
       <c r="F66" s="2" t="n">
@@ -7802,7 +7842,7 @@
         <f>C67-C24</f>
         <v/>
       </c>
-      <c r="E67" s="18" t="n">
+      <c r="E67" s="19" t="n">
         <v>1.182</v>
       </c>
       <c r="F67" s="2" t="n">
@@ -7827,7 +7867,7 @@
         <f>C68-C24</f>
         <v/>
       </c>
-      <c r="E68" s="18" t="n">
+      <c r="E68" s="19" t="n">
         <v>1.182</v>
       </c>
       <c r="F68" s="2" t="n">
@@ -7852,7 +7892,7 @@
         <f>C69-C24</f>
         <v/>
       </c>
-      <c r="E69" s="18" t="n">
+      <c r="E69" s="19" t="n">
         <v>1.182</v>
       </c>
       <c r="F69" s="2" t="n">
@@ -7877,7 +7917,7 @@
         <f>C70-C24</f>
         <v/>
       </c>
-      <c r="E70" s="18" t="n">
+      <c r="E70" s="19" t="n">
         <v>1.093</v>
       </c>
       <c r="F70" s="2" t="n">
@@ -7902,7 +7942,7 @@
         <f>C71-C24</f>
         <v/>
       </c>
-      <c r="E71" s="18" t="n">
+      <c r="E71" s="19" t="n">
         <v>1.093</v>
       </c>
       <c r="F71" s="2" t="n">
@@ -7927,7 +7967,7 @@
         <f>C72-C24</f>
         <v/>
       </c>
-      <c r="E72" s="18" t="n">
+      <c r="E72" s="19" t="n">
         <v>1.093</v>
       </c>
       <c r="F72" s="2" t="n">
@@ -7952,7 +7992,7 @@
         <f>C73-C24</f>
         <v/>
       </c>
-      <c r="E73" s="18" t="n">
+      <c r="E73" s="19" t="n">
         <v>1.093</v>
       </c>
       <c r="F73" s="2" t="n">
@@ -7977,7 +8017,7 @@
         <f>C74-C24</f>
         <v/>
       </c>
-      <c r="E74" s="18" t="n">
+      <c r="E74" s="19" t="n">
         <v>0.925</v>
       </c>
       <c r="F74" s="2" t="n">
@@ -8002,7 +8042,7 @@
         <f>C75-C24</f>
         <v/>
       </c>
-      <c r="E75" s="18" t="n">
+      <c r="E75" s="19" t="n">
         <v>0.925</v>
       </c>
       <c r="F75" s="2" t="n">
@@ -8027,7 +8067,7 @@
         <f>C76-C24</f>
         <v/>
       </c>
-      <c r="E76" s="18" t="n">
+      <c r="E76" s="19" t="n">
         <v>0.925</v>
       </c>
       <c r="F76" s="2" t="n">
@@ -8052,7 +8092,7 @@
         <f>C77-C24</f>
         <v/>
       </c>
-      <c r="E77" s="18" t="n">
+      <c r="E77" s="19" t="n">
         <v>0.925</v>
       </c>
       <c r="F77" s="2" t="n">
@@ -8077,7 +8117,7 @@
         <f>C78-C24</f>
         <v/>
       </c>
-      <c r="E78" s="18" t="n">
+      <c r="E78" s="19" t="n">
         <v>0.516</v>
       </c>
       <c r="F78" s="2" t="n">
@@ -8102,7 +8142,7 @@
         <f>C79-C24</f>
         <v/>
       </c>
-      <c r="E79" s="18" t="n">
+      <c r="E79" s="19" t="n">
         <v>0.516</v>
       </c>
       <c r="F79" s="2" t="n">
@@ -8127,7 +8167,7 @@
         <f>C80-C24</f>
         <v/>
       </c>
-      <c r="E80" s="18" t="n">
+      <c r="E80" s="19" t="n">
         <v>0.516</v>
       </c>
       <c r="F80" s="2" t="n">
@@ -8152,7 +8192,7 @@
         <f>C81-C81</f>
         <v/>
       </c>
-      <c r="E81" s="18" t="n">
+      <c r="E81" s="19" t="n">
         <v>1.054</v>
       </c>
       <c r="F81" s="2" t="n">
@@ -8177,7 +8217,7 @@
         <f>C82-C81</f>
         <v/>
       </c>
-      <c r="E82" s="18" t="n">
+      <c r="E82" s="19" t="n">
         <v>1.054</v>
       </c>
       <c r="F82" s="2" t="n">
@@ -8202,7 +8242,7 @@
         <f>C83-C81</f>
         <v/>
       </c>
-      <c r="E83" s="18" t="n">
+      <c r="E83" s="19" t="n">
         <v>1.083</v>
       </c>
       <c r="F83" s="2" t="n">
@@ -8227,7 +8267,7 @@
         <f>C84-C81</f>
         <v/>
       </c>
-      <c r="E84" s="18" t="n">
+      <c r="E84" s="19" t="n">
         <v>1.083</v>
       </c>
       <c r="F84" s="2" t="n">
@@ -8252,7 +8292,7 @@
         <f>C85-C81</f>
         <v/>
       </c>
-      <c r="E85" s="18" t="n">
+      <c r="E85" s="19" t="n">
         <v>1.083</v>
       </c>
       <c r="F85" s="2" t="n">
@@ -8277,7 +8317,7 @@
         <f>C86-C81</f>
         <v/>
       </c>
-      <c r="E86" s="18" t="n">
+      <c r="E86" s="19" t="n">
         <v>1.083</v>
       </c>
       <c r="F86" s="2" t="n">
@@ -8302,7 +8342,7 @@
         <f>C87-C81</f>
         <v/>
       </c>
-      <c r="E87" s="18" t="n">
+      <c r="E87" s="19" t="n">
         <v>1.098</v>
       </c>
       <c r="F87" s="2" t="n">
@@ -8327,7 +8367,7 @@
         <f>C88-C81</f>
         <v/>
       </c>
-      <c r="E88" s="18" t="n">
+      <c r="E88" s="19" t="n">
         <v>1.098</v>
       </c>
       <c r="F88" s="2" t="n">
@@ -8352,7 +8392,7 @@
         <f>C89-C81</f>
         <v/>
       </c>
-      <c r="E89" s="18" t="n">
+      <c r="E89" s="19" t="n">
         <v>1.098</v>
       </c>
       <c r="F89" s="2" t="n">
@@ -8377,7 +8417,7 @@
         <f>C90-C81</f>
         <v/>
       </c>
-      <c r="E90" s="18" t="n">
+      <c r="E90" s="19" t="n">
         <v>1.098</v>
       </c>
       <c r="F90" s="2" t="n">
@@ -8402,7 +8442,7 @@
         <f>C91-C81</f>
         <v/>
       </c>
-      <c r="E91" s="18" t="n">
+      <c r="E91" s="19" t="n">
         <v>1.135</v>
       </c>
       <c r="F91" s="2" t="n">
@@ -8427,7 +8467,7 @@
         <f>C92-C81</f>
         <v/>
       </c>
-      <c r="E92" s="18" t="n">
+      <c r="E92" s="19" t="n">
         <v>1.135</v>
       </c>
       <c r="F92" s="2" t="n">
@@ -8452,7 +8492,7 @@
         <f>C93-C81</f>
         <v/>
       </c>
-      <c r="E93" s="18" t="n">
+      <c r="E93" s="19" t="n">
         <v>1.135</v>
       </c>
       <c r="F93" s="2" t="n">
@@ -8477,7 +8517,7 @@
         <f>C94-C81</f>
         <v/>
       </c>
-      <c r="E94" s="18" t="n">
+      <c r="E94" s="19" t="n">
         <v>1.135</v>
       </c>
       <c r="F94" s="2" t="n">
@@ -8502,7 +8542,7 @@
         <f>C95-C81</f>
         <v/>
       </c>
-      <c r="E95" s="18" t="n">
+      <c r="E95" s="19" t="n">
         <v>1.285</v>
       </c>
       <c r="F95" s="2" t="n">
@@ -8527,7 +8567,7 @@
         <f>C96-C81</f>
         <v/>
       </c>
-      <c r="E96" s="18" t="n">
+      <c r="E96" s="19" t="n">
         <v>1.285</v>
       </c>
       <c r="F96" s="2" t="n">
@@ -8552,7 +8592,7 @@
         <f>C97-C81</f>
         <v/>
       </c>
-      <c r="E97" s="18" t="n">
+      <c r="E97" s="19" t="n">
         <v>1.285</v>
       </c>
       <c r="F97" s="2" t="n">
@@ -8577,7 +8617,7 @@
         <f>C98-C81</f>
         <v/>
       </c>
-      <c r="E98" s="18" t="n">
+      <c r="E98" s="19" t="n">
         <v>1.285</v>
       </c>
       <c r="F98" s="2" t="n">
@@ -8602,7 +8642,7 @@
         <f>C99-C81</f>
         <v/>
       </c>
-      <c r="E99" s="18" t="n">
+      <c r="E99" s="19" t="n">
         <v>1.54</v>
       </c>
       <c r="F99" s="2" t="n">
@@ -8627,7 +8667,7 @@
         <f>C100-C81</f>
         <v/>
       </c>
-      <c r="E100" s="18" t="n">
+      <c r="E100" s="19" t="n">
         <v>1.54</v>
       </c>
       <c r="F100" s="2" t="n">
@@ -8652,7 +8692,7 @@
         <f>C101-C81</f>
         <v/>
       </c>
-      <c r="E101" s="18" t="n">
+      <c r="E101" s="19" t="n">
         <v>1.54</v>
       </c>
       <c r="F101" s="2" t="n">
@@ -8677,7 +8717,7 @@
         <f>C102-C81</f>
         <v/>
       </c>
-      <c r="E102" s="18" t="n">
+      <c r="E102" s="19" t="n">
         <v>1.54</v>
       </c>
       <c r="F102" s="2" t="n">
@@ -8702,7 +8742,7 @@
         <f>C103-C81</f>
         <v/>
       </c>
-      <c r="E103" s="18" t="n">
+      <c r="E103" s="19" t="n">
         <v>1.337</v>
       </c>
       <c r="F103" s="2" t="n">
@@ -8727,7 +8767,7 @@
         <f>C104-C81</f>
         <v/>
       </c>
-      <c r="E104" s="18" t="n">
+      <c r="E104" s="19" t="n">
         <v>1.337</v>
       </c>
       <c r="F104" s="2" t="n">
@@ -8752,7 +8792,7 @@
         <f>C105-C81</f>
         <v/>
       </c>
-      <c r="E105" s="18" t="n">
+      <c r="E105" s="19" t="n">
         <v>1.337</v>
       </c>
       <c r="F105" s="2" t="n">
@@ -8777,7 +8817,7 @@
         <f>C106-C81</f>
         <v/>
       </c>
-      <c r="E106" s="18" t="n">
+      <c r="E106" s="19" t="n">
         <v>1.337</v>
       </c>
       <c r="F106" s="2" t="n">
@@ -8802,7 +8842,7 @@
         <f>C107-C81</f>
         <v/>
       </c>
-      <c r="E107" s="18" t="n">
+      <c r="E107" s="19" t="n">
         <v>0.91</v>
       </c>
       <c r="F107" s="2" t="n">
@@ -8827,7 +8867,7 @@
         <f>C108-C81</f>
         <v/>
       </c>
-      <c r="E108" s="18" t="n">
+      <c r="E108" s="19" t="n">
         <v>0.91</v>
       </c>
       <c r="F108" s="2" t="n">
@@ -8852,7 +8892,7 @@
         <f>C109-C81</f>
         <v/>
       </c>
-      <c r="E109" s="18" t="n">
+      <c r="E109" s="19" t="n">
         <v>0.91</v>
       </c>
       <c r="F109" s="2" t="n">
@@ -8877,7 +8917,7 @@
         <f>C110-C81</f>
         <v/>
       </c>
-      <c r="E110" s="18" t="n">
+      <c r="E110" s="19" t="n">
         <v>0.91</v>
       </c>
       <c r="F110" s="2" t="n">
@@ -8902,7 +8942,7 @@
         <f>C111-C81</f>
         <v/>
       </c>
-      <c r="E111" s="18" t="n">
+      <c r="E111" s="19" t="n">
         <v>0.789</v>
       </c>
       <c r="F111" s="2" t="n">
@@ -8927,7 +8967,7 @@
         <f>C112-C112</f>
         <v/>
       </c>
-      <c r="E112" s="18" t="n">
+      <c r="E112" s="19" t="n">
         <v>0.395</v>
       </c>
       <c r="F112" s="2" t="n">
@@ -8952,7 +8992,7 @@
         <f>C113-C112</f>
         <v/>
       </c>
-      <c r="E113" s="18" t="n">
+      <c r="E113" s="19" t="n">
         <v>0.468</v>
       </c>
       <c r="F113" s="2" t="n">
@@ -8977,7 +9017,7 @@
         <f>C114-C112</f>
         <v/>
       </c>
-      <c r="E114" s="18" t="n">
+      <c r="E114" s="19" t="n">
         <v>0.468</v>
       </c>
       <c r="F114" s="2" t="n">
@@ -9002,7 +9042,7 @@
         <f>C115-C112</f>
         <v/>
       </c>
-      <c r="E115" s="18" t="n">
+      <c r="E115" s="19" t="n">
         <v>0.468</v>
       </c>
       <c r="F115" s="2" t="n">
@@ -9027,7 +9067,7 @@
         <f>C116-C112</f>
         <v/>
       </c>
-      <c r="E116" s="18" t="n">
+      <c r="E116" s="19" t="n">
         <v>0.468</v>
       </c>
       <c r="F116" s="2" t="n">
@@ -9052,7 +9092,7 @@
         <f>C117-C112</f>
         <v/>
       </c>
-      <c r="E117" s="18" t="n">
+      <c r="E117" s="19" t="n">
         <v>0.505</v>
       </c>
       <c r="F117" s="2" t="n">
@@ -9077,7 +9117,7 @@
         <f>C118-C112</f>
         <v/>
       </c>
-      <c r="E118" s="18" t="n">
+      <c r="E118" s="19" t="n">
         <v>0.505</v>
       </c>
       <c r="F118" s="2" t="n">
@@ -9102,7 +9142,7 @@
         <f>C119-C112</f>
         <v/>
       </c>
-      <c r="E119" s="18" t="n">
+      <c r="E119" s="19" t="n">
         <v>0.505</v>
       </c>
       <c r="F119" s="2" t="n">
@@ -9127,7 +9167,7 @@
         <f>C120-C112</f>
         <v/>
       </c>
-      <c r="E120" s="18" t="n">
+      <c r="E120" s="19" t="n">
         <v>0.505</v>
       </c>
       <c r="F120" s="2" t="n">
@@ -9152,7 +9192,7 @@
         <f>C121-C112</f>
         <v/>
       </c>
-      <c r="E121" s="18" t="n">
+      <c r="E121" s="19" t="n">
         <v>0.653</v>
       </c>
       <c r="F121" s="2" t="n">
@@ -9177,7 +9217,7 @@
         <f>C122-C112</f>
         <v/>
       </c>
-      <c r="E122" s="18" t="n">
+      <c r="E122" s="19" t="n">
         <v>0.653</v>
       </c>
       <c r="F122" s="2" t="n">
@@ -9202,7 +9242,7 @@
         <f>C123-C112</f>
         <v/>
       </c>
-      <c r="E123" s="18" t="n">
+      <c r="E123" s="19" t="n">
         <v>0.653</v>
       </c>
       <c r="F123" s="2" t="n">
@@ -9227,7 +9267,7 @@
         <f>C124-C112</f>
         <v/>
       </c>
-      <c r="E124" s="18" t="n">
+      <c r="E124" s="19" t="n">
         <v>0.653</v>
       </c>
       <c r="F124" s="2" t="n">
@@ -9252,7 +9292,7 @@
         <f>C125-C112</f>
         <v/>
       </c>
-      <c r="E125" s="18" t="n">
+      <c r="E125" s="19" t="n">
         <v>0.866</v>
       </c>
       <c r="F125" s="2" t="n">
@@ -9277,7 +9317,7 @@
         <f>C126-C112</f>
         <v/>
       </c>
-      <c r="E126" s="18" t="n">
+      <c r="E126" s="19" t="n">
         <v>0.866</v>
       </c>
       <c r="F126" s="2" t="n">
@@ -9302,7 +9342,7 @@
         <f>C127-C112</f>
         <v/>
       </c>
-      <c r="E127" s="18" t="n">
+      <c r="E127" s="19" t="n">
         <v>0.866</v>
       </c>
       <c r="F127" s="2" t="n">
@@ -9327,7 +9367,7 @@
         <f>C128-C112</f>
         <v/>
       </c>
-      <c r="E128" s="18" t="n">
+      <c r="E128" s="19" t="n">
         <v>0.866</v>
       </c>
       <c r="F128" s="2" t="n">
@@ -9352,7 +9392,7 @@
         <f>C129-C112</f>
         <v/>
       </c>
-      <c r="E129" s="18" t="n">
+      <c r="E129" s="19" t="n">
         <v>0.95</v>
       </c>
       <c r="F129" s="2" t="n">
@@ -9377,7 +9417,7 @@
         <f>C130-C112</f>
         <v/>
       </c>
-      <c r="E130" s="18" t="n">
+      <c r="E130" s="19" t="n">
         <v>0.95</v>
       </c>
       <c r="F130" s="2" t="n">
@@ -9402,7 +9442,7 @@
         <f>C131-C112</f>
         <v/>
       </c>
-      <c r="E131" s="18" t="n">
+      <c r="E131" s="19" t="n">
         <v>0.95</v>
       </c>
       <c r="F131" s="2" t="n">
@@ -9427,7 +9467,7 @@
         <f>C132-C112</f>
         <v/>
       </c>
-      <c r="E132" s="18" t="n">
+      <c r="E132" s="19" t="n">
         <v>0.95</v>
       </c>
       <c r="F132" s="2" t="n">
@@ -9452,7 +9492,7 @@
         <f>C133-C112</f>
         <v/>
       </c>
-      <c r="E133" s="18" t="n">
+      <c r="E133" s="19" t="n">
         <v>1.114</v>
       </c>
       <c r="F133" s="2" t="n">
@@ -9477,7 +9517,7 @@
         <f>C134-C112</f>
         <v/>
       </c>
-      <c r="E134" s="18" t="n">
+      <c r="E134" s="19" t="n">
         <v>1.114</v>
       </c>
       <c r="F134" s="2" t="n">
@@ -9502,7 +9542,7 @@
         <f>C135-C112</f>
         <v/>
       </c>
-      <c r="E135" s="18" t="n">
+      <c r="E135" s="19" t="n">
         <v>1.114</v>
       </c>
       <c r="F135" s="2" t="n">
@@ -9527,7 +9567,7 @@
         <f>C136-C112</f>
         <v/>
       </c>
-      <c r="E136" s="18" t="n">
+      <c r="E136" s="19" t="n">
         <v>1.114</v>
       </c>
       <c r="F136" s="2" t="n">
@@ -9552,7 +9592,7 @@
         <f>C137-C112</f>
         <v/>
       </c>
-      <c r="E137" s="18" t="n">
+      <c r="E137" s="19" t="n">
         <v>0.775</v>
       </c>
       <c r="F137" s="2" t="n">
@@ -9577,7 +9617,7 @@
         <f>C138-C112</f>
         <v/>
       </c>
-      <c r="E138" s="18" t="n">
+      <c r="E138" s="19" t="n">
         <v>0.775</v>
       </c>
       <c r="F138" s="2" t="n">
@@ -9602,7 +9642,7 @@
         <f>C139-C112</f>
         <v/>
       </c>
-      <c r="E139" s="18" t="n">
+      <c r="E139" s="19" t="n">
         <v>0.775</v>
       </c>
       <c r="F139" s="2" t="n">
@@ -9627,7 +9667,7 @@
         <f>C140-C112</f>
         <v/>
       </c>
-      <c r="E140" s="18" t="n">
+      <c r="E140" s="19" t="n">
         <v>0.775</v>
       </c>
       <c r="F140" s="2" t="n">
@@ -9652,7 +9692,7 @@
         <f>C141-C112</f>
         <v/>
       </c>
-      <c r="E141" s="18" t="n">
+      <c r="E141" s="19" t="n">
         <v>0.852</v>
       </c>
       <c r="F141" s="2" t="n">
@@ -9677,7 +9717,7 @@
         <f>C142-C112</f>
         <v/>
       </c>
-      <c r="E142" s="18" t="n">
+      <c r="E142" s="19" t="n">
         <v>0.852</v>
       </c>
       <c r="F142" s="2" t="n">
@@ -9702,7 +9742,7 @@
         <f>C143-C112</f>
         <v/>
       </c>
-      <c r="E143" s="18" t="n">
+      <c r="E143" s="19" t="n">
         <v>0.852</v>
       </c>
       <c r="F143" s="2" t="n">
@@ -9727,7 +9767,7 @@
         <f>C144-C112</f>
         <v/>
       </c>
-      <c r="E144" s="18" t="n">
+      <c r="E144" s="19" t="n">
         <v>0.852</v>
       </c>
       <c r="F144" s="2" t="n">
@@ -9752,7 +9792,7 @@
         <f>C145-C112</f>
         <v/>
       </c>
-      <c r="E145" s="18" t="n">
+      <c r="E145" s="19" t="n">
         <v>1.034</v>
       </c>
       <c r="F145" s="2" t="n">
@@ -9777,7 +9817,7 @@
         <f>C146-C112</f>
         <v/>
       </c>
-      <c r="E146" s="18" t="n">
+      <c r="E146" s="19" t="n">
         <v>1.034</v>
       </c>
       <c r="F146" s="2" t="n">
@@ -9802,7 +9842,7 @@
         <f>C147-C112</f>
         <v/>
       </c>
-      <c r="E147" s="18" t="n">
+      <c r="E147" s="19" t="n">
         <v>1.034</v>
       </c>
       <c r="F147" s="2" t="n">
@@ -9827,7 +9867,7 @@
         <f>C148-C112</f>
         <v/>
       </c>
-      <c r="E148" s="18" t="n">
+      <c r="E148" s="19" t="n">
         <v>1.034</v>
       </c>
       <c r="F148" s="2" t="n">
@@ -9852,7 +9892,7 @@
         <f>C149-C112</f>
         <v/>
       </c>
-      <c r="E149" s="18" t="n">
+      <c r="E149" s="19" t="n">
         <v>1.259</v>
       </c>
       <c r="F149" s="2" t="n">
@@ -9877,7 +9917,7 @@
         <f>C150-C112</f>
         <v/>
       </c>
-      <c r="E150" s="18" t="n">
+      <c r="E150" s="19" t="n">
         <v>1.259</v>
       </c>
       <c r="F150" s="2" t="n">
@@ -9902,7 +9942,7 @@
         <f>C151-C112</f>
         <v/>
       </c>
-      <c r="E151" s="18" t="n">
+      <c r="E151" s="19" t="n">
         <v>1.259</v>
       </c>
       <c r="F151" s="2" t="n">
@@ -9927,7 +9967,7 @@
         <f>C152-C112</f>
         <v/>
       </c>
-      <c r="E152" s="18" t="n">
+      <c r="E152" s="19" t="n">
         <v>1.259</v>
       </c>
       <c r="F152" s="2" t="n">
@@ -9952,7 +9992,7 @@
         <f>C153-C112</f>
         <v/>
       </c>
-      <c r="E153" s="18" t="n">
+      <c r="E153" s="19" t="n">
         <v>1.249</v>
       </c>
       <c r="F153" s="2" t="n">
@@ -9977,7 +10017,7 @@
         <f>C154-C112</f>
         <v/>
       </c>
-      <c r="E154" s="18" t="n">
+      <c r="E154" s="19" t="n">
         <v>1.249</v>
       </c>
       <c r="F154" s="2" t="n">
@@ -10002,7 +10042,7 @@
         <f>C155-C112</f>
         <v/>
       </c>
-      <c r="E155" s="18" t="n">
+      <c r="E155" s="19" t="n">
         <v>1.249</v>
       </c>
       <c r="F155" s="2" t="n">
@@ -10027,7 +10067,7 @@
         <f>C156-C112</f>
         <v/>
       </c>
-      <c r="E156" s="18" t="n">
+      <c r="E156" s="19" t="n">
         <v>1.249</v>
       </c>
       <c r="F156" s="2" t="n">
@@ -10052,7 +10092,7 @@
         <f>C157-C112</f>
         <v/>
       </c>
-      <c r="E157" s="18" t="n">
+      <c r="E157" s="19" t="n">
         <v>1.415</v>
       </c>
       <c r="F157" s="2" t="n">
@@ -10077,7 +10117,7 @@
         <f>C158-C112</f>
         <v/>
       </c>
-      <c r="E158" s="18" t="n">
+      <c r="E158" s="19" t="n">
         <v>1.415</v>
       </c>
       <c r="F158" s="2" t="n">
@@ -10102,7 +10142,7 @@
         <f>C159-C112</f>
         <v/>
       </c>
-      <c r="E159" s="18" t="n">
+      <c r="E159" s="19" t="n">
         <v>1.415</v>
       </c>
       <c r="F159" s="2" t="n">
@@ -10127,7 +10167,7 @@
         <f>C160-C112</f>
         <v/>
       </c>
-      <c r="E160" s="18" t="n">
+      <c r="E160" s="19" t="n">
         <v>1.415</v>
       </c>
       <c r="F160" s="2" t="n">
@@ -10152,7 +10192,7 @@
         <f>C161-C112</f>
         <v/>
       </c>
-      <c r="E161" s="18" t="n">
+      <c r="E161" s="19" t="n">
         <v>0.979</v>
       </c>
       <c r="F161" s="2" t="n">
@@ -10177,7 +10217,7 @@
         <f>C162-C112</f>
         <v/>
       </c>
-      <c r="E162" s="18" t="n">
+      <c r="E162" s="19" t="n">
         <v>0.979</v>
       </c>
       <c r="F162" s="2" t="n">
@@ -10202,7 +10242,7 @@
         <f>C163-C112</f>
         <v/>
       </c>
-      <c r="E163" s="18" t="n">
+      <c r="E163" s="19" t="n">
         <v>0.979</v>
       </c>
       <c r="F163" s="2" t="n">
@@ -10227,7 +10267,7 @@
         <f>C164-C112</f>
         <v/>
       </c>
-      <c r="E164" s="18" t="n">
+      <c r="E164" s="19" t="n">
         <v>0.979</v>
       </c>
       <c r="F164" s="2" t="n">
@@ -10252,7 +10292,7 @@
         <f>C165-C112</f>
         <v/>
       </c>
-      <c r="E165" s="18" t="n">
+      <c r="E165" s="19" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="F165" s="2" t="n">
@@ -10277,7 +10317,7 @@
         <f>C166-C112</f>
         <v/>
       </c>
-      <c r="E166" s="18" t="n">
+      <c r="E166" s="19" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="F166" s="2" t="n">
@@ -10302,7 +10342,7 @@
         <f>C167-C112</f>
         <v/>
       </c>
-      <c r="E167" s="18" t="n">
+      <c r="E167" s="19" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="F167" s="2" t="n">
@@ -10327,7 +10367,7 @@
         <f>C168-C112</f>
         <v/>
       </c>
-      <c r="E168" s="18" t="n">
+      <c r="E168" s="19" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="F168" s="2" t="n">
@@ -10352,7 +10392,7 @@
         <f>C169-C169</f>
         <v/>
       </c>
-      <c r="E169" s="18" t="n">
+      <c r="E169" s="19" t="n">
         <v>0.616</v>
       </c>
     </row>
@@ -10374,7 +10414,7 @@
         <f>C170-C169</f>
         <v/>
       </c>
-      <c r="E170" s="18" t="n">
+      <c r="E170" s="19" t="n">
         <v>0.637</v>
       </c>
     </row>
@@ -10396,7 +10436,7 @@
         <f>C171-C169</f>
         <v/>
       </c>
-      <c r="E171" s="18" t="n">
+      <c r="E171" s="19" t="n">
         <v>0.64</v>
       </c>
     </row>
@@ -10418,7 +10458,7 @@
         <f>C172-C169</f>
         <v/>
       </c>
-      <c r="E172" s="18" t="n">
+      <c r="E172" s="19" t="n">
         <v>0.655</v>
       </c>
     </row>
@@ -10440,7 +10480,7 @@
         <f>C173-C169</f>
         <v/>
       </c>
-      <c r="E173" s="18" t="n">
+      <c r="E173" s="19" t="n">
         <v>0.627</v>
       </c>
     </row>
@@ -10462,7 +10502,7 @@
         <f>C174-C169</f>
         <v/>
       </c>
-      <c r="E174" s="18" t="n">
+      <c r="E174" s="19" t="n">
         <v>0.614</v>
       </c>
     </row>
@@ -10484,7 +10524,7 @@
         <f>C175-C169</f>
         <v/>
       </c>
-      <c r="E175" s="18" t="n">
+      <c r="E175" s="19" t="n">
         <v>0.592</v>
       </c>
     </row>
@@ -10506,7 +10546,7 @@
         <f>C176-C169</f>
         <v/>
       </c>
-      <c r="E176" s="18" t="n">
+      <c r="E176" s="19" t="n">
         <v>0.595</v>
       </c>
     </row>
@@ -10528,7 +10568,7 @@
         <f>C177-C169</f>
         <v/>
       </c>
-      <c r="E177" s="18" t="n">
+      <c r="E177" s="19" t="n">
         <v>0.596</v>
       </c>
     </row>
@@ -10550,7 +10590,7 @@
         <f>C178-C169</f>
         <v/>
       </c>
-      <c r="E178" s="18" t="n">
+      <c r="E178" s="19" t="n">
         <v>0.6860000000000001</v>
       </c>
     </row>
@@ -10572,7 +10612,7 @@
         <f>C179-C169</f>
         <v/>
       </c>
-      <c r="E179" s="18" t="n">
+      <c r="E179" s="19" t="n">
         <v>0.78</v>
       </c>
     </row>
@@ -10594,7 +10634,7 @@
         <f>C180-C169</f>
         <v/>
       </c>
-      <c r="E180" s="18" t="n">
+      <c r="E180" s="19" t="n">
         <v>0.896</v>
       </c>
     </row>
@@ -10616,7 +10656,7 @@
         <f>C181-C169</f>
         <v/>
       </c>
-      <c r="E181" s="18" t="n">
+      <c r="E181" s="19" t="n">
         <v>1.013</v>
       </c>
     </row>
@@ -10638,7 +10678,7 @@
         <f>C182-C169</f>
         <v/>
       </c>
-      <c r="E182" s="18" t="n">
+      <c r="E182" s="19" t="n">
         <v>1.147</v>
       </c>
     </row>
@@ -10660,7 +10700,7 @@
         <f>C183-C169</f>
         <v/>
       </c>
-      <c r="E183" s="18" t="n">
+      <c r="E183" s="19" t="n">
         <v>1.334</v>
       </c>
     </row>
@@ -10682,7 +10722,7 @@
         <f>C184-C169</f>
         <v/>
       </c>
-      <c r="E184" s="18" t="n">
+      <c r="E184" s="19" t="n">
         <v>1.558</v>
       </c>
     </row>
@@ -10704,7 +10744,7 @@
         <f>C185-C169</f>
         <v/>
       </c>
-      <c r="E185" s="18" t="n">
+      <c r="E185" s="19" t="n">
         <v>1.702</v>
       </c>
     </row>
@@ -10726,7 +10766,7 @@
         <f>C186-C186</f>
         <v/>
       </c>
-      <c r="E186" s="18" t="n">
+      <c r="E186" s="19" t="n">
         <v>0.537</v>
       </c>
     </row>
@@ -10748,7 +10788,7 @@
         <f>C187-C186</f>
         <v/>
       </c>
-      <c r="E187" s="18" t="n">
+      <c r="E187" s="19" t="n">
         <v>0.5639999999999999</v>
       </c>
     </row>
@@ -10770,7 +10810,7 @@
         <f>C188-C186</f>
         <v/>
       </c>
-      <c r="E188" s="18" t="n">
+      <c r="E188" s="19" t="n">
         <v>0.595</v>
       </c>
     </row>
@@ -10792,7 +10832,7 @@
         <f>C189-C186</f>
         <v/>
       </c>
-      <c r="E189" s="18" t="n">
+      <c r="E189" s="19" t="n">
         <v>0.611</v>
       </c>
     </row>
@@ -10814,7 +10854,7 @@
         <f>C190-C186</f>
         <v/>
       </c>
-      <c r="E190" s="18" t="n">
+      <c r="E190" s="19" t="n">
         <v>0.569</v>
       </c>
     </row>
@@ -10836,7 +10876,7 @@
         <f>C191-C186</f>
         <v/>
       </c>
-      <c r="E191" s="18" t="n">
+      <c r="E191" s="19" t="n">
         <v>0.555</v>
       </c>
     </row>
@@ -10858,7 +10898,7 @@
         <f>C192-C186</f>
         <v/>
       </c>
-      <c r="E192" s="18" t="n">
+      <c r="E192" s="19" t="n">
         <v>0.542</v>
       </c>
     </row>
@@ -10880,7 +10920,7 @@
         <f>C193-C186</f>
         <v/>
       </c>
-      <c r="E193" s="18" t="n">
+      <c r="E193" s="19" t="n">
         <v>0.551</v>
       </c>
     </row>
@@ -10902,7 +10942,7 @@
         <f>C194-C186</f>
         <v/>
       </c>
-      <c r="E194" s="18" t="n">
+      <c r="E194" s="19" t="n">
         <v>0.5620000000000001</v>
       </c>
     </row>
@@ -10924,7 +10964,7 @@
         <f>C195-C186</f>
         <v/>
       </c>
-      <c r="E195" s="18" t="n">
+      <c r="E195" s="19" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -10946,7 +10986,7 @@
         <f>C196-C186</f>
         <v/>
       </c>
-      <c r="E196" s="18" t="n">
+      <c r="E196" s="19" t="n">
         <v>0.715</v>
       </c>
     </row>
@@ -10968,7 +11008,7 @@
         <f>C197-C186</f>
         <v/>
       </c>
-      <c r="E197" s="18" t="n">
+      <c r="E197" s="19" t="n">
         <v>0.829</v>
       </c>
     </row>
@@ -10990,7 +11030,7 @@
         <f>C198-C186</f>
         <v/>
       </c>
-      <c r="E198" s="18" t="n">
+      <c r="E198" s="19" t="n">
         <v>0.901</v>
       </c>
     </row>
@@ -11012,7 +11052,7 @@
         <f>C199-C186</f>
         <v/>
       </c>
-      <c r="E199" s="18" t="n">
+      <c r="E199" s="19" t="n">
         <v>1.036</v>
       </c>
     </row>
@@ -11034,7 +11074,7 @@
         <f>C200-C186</f>
         <v/>
       </c>
-      <c r="E200" s="18" t="n">
+      <c r="E200" s="19" t="n">
         <v>1.187</v>
       </c>
     </row>
@@ -11056,7 +11096,7 @@
         <f>C201-C186</f>
         <v/>
       </c>
-      <c r="E201" s="18" t="n">
+      <c r="E201" s="19" t="n">
         <v>1.379</v>
       </c>
     </row>
@@ -11078,7 +11118,7 @@
         <f>C202-C186</f>
         <v/>
       </c>
-      <c r="E202" s="18" t="n">
+      <c r="E202" s="19" t="n">
         <v>1.536</v>
       </c>
     </row>
@@ -11137,7 +11177,7 @@
       <c r="A2" s="2" t="n">
         <v>1899</v>
       </c>
-      <c r="B2" s="18" t="n">
+      <c r="B2" s="19" t="n">
         <v>1.169</v>
       </c>
     </row>
@@ -11145,7 +11185,7 @@
       <c r="A3" s="2" t="n">
         <v>1900</v>
       </c>
-      <c r="B3" s="18" t="n">
+      <c r="B3" s="19" t="n">
         <v>1.247</v>
       </c>
     </row>
@@ -11153,7 +11193,7 @@
       <c r="A4" s="2" t="n">
         <v>1901</v>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="19" t="n">
         <v>1.047</v>
       </c>
     </row>
@@ -11161,7 +11201,7 @@
       <c r="A5" s="2" t="n">
         <v>1902</v>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="19" t="n">
         <v>1.068</v>
       </c>
     </row>
@@ -11169,7 +11209,7 @@
       <c r="A6" s="2" t="n">
         <v>1903</v>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="19" t="n">
         <v>1.068</v>
       </c>
     </row>
@@ -11177,7 +11217,7 @@
       <c r="A7" s="2" t="n">
         <v>1904</v>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="19" t="n">
         <v>1.252</v>
       </c>
     </row>
@@ -11185,7 +11225,7 @@
       <c r="A8" s="2" t="n">
         <v>1905</v>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="19" t="n">
         <v>1.49</v>
       </c>
     </row>
@@ -11193,7 +11233,7 @@
       <c r="A9" s="2" t="n">
         <v>1906</v>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="19" t="n">
         <v>1.798</v>
       </c>
     </row>
@@ -11201,7 +11241,7 @@
       <c r="A10" s="2" t="n">
         <v>1907</v>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="19" t="n">
         <v>2.026</v>
       </c>
     </row>
@@ -11209,7 +11249,7 @@
       <c r="A11" s="2" t="n">
         <v>1908</v>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="19" t="n">
         <v>2.221</v>
       </c>
     </row>
@@ -11217,7 +11257,7 @@
       <c r="A12" s="2" t="n">
         <v>1909</v>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="19" t="n">
         <v>2.115</v>
       </c>
     </row>
@@ -11225,7 +11265,7 @@
       <c r="A13" s="2" t="n">
         <v>1910</v>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>2.303</v>
       </c>
     </row>
@@ -11233,7 +11273,7 @@
       <c r="A14" s="2" t="n">
         <v>1911</v>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="19" t="n">
         <v>2.117</v>
       </c>
     </row>
@@ -11241,7 +11281,7 @@
       <c r="A15" s="2" t="n">
         <v>1912</v>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="19" t="n">
         <v>1.998</v>
       </c>
     </row>
@@ -11249,7 +11289,7 @@
       <c r="A16" s="2" t="n">
         <v>1913</v>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="19" t="n">
         <v>1.979</v>
       </c>
     </row>
@@ -11257,7 +11297,7 @@
       <c r="A17" s="2" t="n">
         <v>1914</v>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="19" t="n">
         <v>1.418</v>
       </c>
     </row>
@@ -11265,7 +11305,7 @@
       <c r="A18" s="2" t="n">
         <v>1915</v>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="19" t="n">
         <v>0.79</v>
       </c>
     </row>
@@ -11273,7 +11313,7 @@
       <c r="A19" s="2" t="n">
         <v>1916</v>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="19" t="n">
         <v>0.8159999999999999</v>
       </c>
     </row>
@@ -11281,7 +11321,7 @@
       <c r="A20" s="2" t="n">
         <v>1917</v>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="19" t="n">
         <v>1.013</v>
       </c>
     </row>
@@ -11289,7 +11329,7 @@
       <c r="A21" s="2" t="n">
         <v>1918</v>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="19" t="n">
         <v>0.78</v>
       </c>
     </row>
@@ -11297,7 +11337,7 @@
       <c r="A22" s="2" t="n">
         <v>1919</v>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="19" t="n">
         <v>0.508</v>
       </c>
     </row>
@@ -11305,7 +11345,7 @@
       <c r="A23" s="2" t="n">
         <v>1920</v>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="19" t="n">
         <v>0.726</v>
       </c>
     </row>
@@ -11313,7 +11353,7 @@
       <c r="A24" s="2" t="n">
         <v>1972</v>
       </c>
-      <c r="C24" s="18" t="n">
+      <c r="C24" s="19" t="n">
         <v>0.379</v>
       </c>
     </row>
@@ -11321,7 +11361,7 @@
       <c r="A25" s="2" t="n">
         <v>1973</v>
       </c>
-      <c r="C25" s="18" t="n">
+      <c r="C25" s="19" t="n">
         <v>0.391</v>
       </c>
     </row>
@@ -11329,7 +11369,7 @@
       <c r="A26" s="2" t="n">
         <v>1974</v>
       </c>
-      <c r="C26" s="18" t="n">
+      <c r="C26" s="19" t="n">
         <v>0.495</v>
       </c>
     </row>
@@ -11337,7 +11377,7 @@
       <c r="A27" s="2" t="n">
         <v>1975</v>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C27" s="19" t="n">
         <v>0.665</v>
       </c>
     </row>
@@ -11345,7 +11385,7 @@
       <c r="A28" s="2" t="n">
         <v>1976</v>
       </c>
-      <c r="C28" s="18" t="n">
+      <c r="C28" s="19" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -11353,7 +11393,7 @@
       <c r="A29" s="2" t="n">
         <v>1977</v>
       </c>
-      <c r="C29" s="18" t="n">
+      <c r="C29" s="19" t="n">
         <v>0.722</v>
       </c>
     </row>
@@ -11361,7 +11401,7 @@
       <c r="A30" s="2" t="n">
         <v>1978</v>
       </c>
-      <c r="C30" s="18" t="n">
+      <c r="C30" s="19" t="n">
         <v>0.909</v>
       </c>
     </row>
@@ -11369,7 +11409,7 @@
       <c r="A31" s="2" t="n">
         <v>1979</v>
       </c>
-      <c r="C31" s="18" t="n">
+      <c r="C31" s="19" t="n">
         <v>1.064</v>
       </c>
     </row>
@@ -11377,7 +11417,7 @@
       <c r="A32" s="2" t="n">
         <v>1980</v>
       </c>
-      <c r="C32" s="18" t="n">
+      <c r="C32" s="19" t="n">
         <v>1.425</v>
       </c>
     </row>
@@ -11385,7 +11425,7 @@
       <c r="A33" s="2" t="n">
         <v>1981</v>
       </c>
-      <c r="C33" s="18" t="n">
+      <c r="C33" s="19" t="n">
         <v>1.972</v>
       </c>
     </row>
@@ -11393,7 +11433,7 @@
       <c r="A34" s="2" t="n">
         <v>1982</v>
       </c>
-      <c r="C34" s="18" t="n">
+      <c r="C34" s="19" t="n">
         <v>1.891</v>
       </c>
     </row>
@@ -11401,7 +11441,7 @@
       <c r="A35" s="2" t="n">
         <v>1983</v>
       </c>
-      <c r="C35" s="18" t="n">
+      <c r="C35" s="19" t="n">
         <v>1.182</v>
       </c>
     </row>
@@ -11409,7 +11449,7 @@
       <c r="A36" s="2" t="n">
         <v>1984</v>
       </c>
-      <c r="C36" s="18" t="n">
+      <c r="C36" s="19" t="n">
         <v>1.093</v>
       </c>
     </row>
@@ -11417,7 +11457,7 @@
       <c r="A37" s="2" t="n">
         <v>1985</v>
       </c>
-      <c r="C37" s="18" t="n">
+      <c r="C37" s="19" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -11425,7 +11465,7 @@
       <c r="A38" s="2" t="n">
         <v>1986</v>
       </c>
-      <c r="C38" s="18" t="n">
+      <c r="C38" s="19" t="n">
         <v>0.516</v>
       </c>
     </row>
@@ -11433,7 +11473,7 @@
       <c r="A39" s="2" t="n">
         <v>1995</v>
       </c>
-      <c r="D39" s="18" t="n">
+      <c r="D39" s="19" t="n">
         <v>1.054</v>
       </c>
     </row>
@@ -11441,7 +11481,7 @@
       <c r="A40" s="2" t="n">
         <v>1996</v>
       </c>
-      <c r="D40" s="18" t="n">
+      <c r="D40" s="19" t="n">
         <v>1.083</v>
       </c>
     </row>
@@ -11449,7 +11489,7 @@
       <c r="A41" s="2" t="n">
         <v>1997</v>
       </c>
-      <c r="D41" s="18" t="n">
+      <c r="D41" s="19" t="n">
         <v>1.098</v>
       </c>
     </row>
@@ -11457,7 +11497,7 @@
       <c r="A42" s="2" t="n">
         <v>1998</v>
       </c>
-      <c r="D42" s="18" t="n">
+      <c r="D42" s="19" t="n">
         <v>1.135</v>
       </c>
     </row>
@@ -11465,7 +11505,7 @@
       <c r="A43" s="2" t="n">
         <v>1999</v>
       </c>
-      <c r="D43" s="18" t="n">
+      <c r="D43" s="19" t="n">
         <v>1.285</v>
       </c>
     </row>
@@ -11473,7 +11513,7 @@
       <c r="A44" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="D44" s="18" t="n">
+      <c r="D44" s="19" t="n">
         <v>1.54</v>
       </c>
     </row>
@@ -11481,7 +11521,7 @@
       <c r="A45" s="2" t="n">
         <v>2001</v>
       </c>
-      <c r="D45" s="18" t="n">
+      <c r="D45" s="19" t="n">
         <v>1.337</v>
       </c>
     </row>
@@ -11489,10 +11529,10 @@
       <c r="A46" s="2" t="n">
         <v>2002</v>
       </c>
-      <c r="D46" s="18" t="n">
+      <c r="D46" s="19" t="n">
         <v>0.91</v>
       </c>
-      <c r="E46" s="18" t="n">
+      <c r="E46" s="19" t="n">
         <v>0.395</v>
       </c>
     </row>
@@ -11500,10 +11540,10 @@
       <c r="A47" s="2" t="n">
         <v>2003</v>
       </c>
-      <c r="D47" s="18" t="n">
+      <c r="D47" s="19" t="n">
         <v>0.789</v>
       </c>
-      <c r="E47" s="18" t="n">
+      <c r="E47" s="19" t="n">
         <v>0.468</v>
       </c>
     </row>
@@ -11511,7 +11551,7 @@
       <c r="A48" s="2" t="n">
         <v>2004</v>
       </c>
-      <c r="E48" s="18" t="n">
+      <c r="E48" s="19" t="n">
         <v>0.505</v>
       </c>
     </row>
@@ -11519,7 +11559,7 @@
       <c r="A49" s="2" t="n">
         <v>2005</v>
       </c>
-      <c r="E49" s="18" t="n">
+      <c r="E49" s="19" t="n">
         <v>0.653</v>
       </c>
     </row>
@@ -11527,7 +11567,7 @@
       <c r="A50" s="2" t="n">
         <v>2006</v>
       </c>
-      <c r="E50" s="18" t="n">
+      <c r="E50" s="19" t="n">
         <v>0.866</v>
       </c>
     </row>
@@ -11535,7 +11575,7 @@
       <c r="A51" s="2" t="n">
         <v>2007</v>
       </c>
-      <c r="E51" s="18" t="n">
+      <c r="E51" s="19" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -11543,7 +11583,7 @@
       <c r="A52" s="2" t="n">
         <v>2008</v>
       </c>
-      <c r="E52" s="18" t="n">
+      <c r="E52" s="19" t="n">
         <v>1.114</v>
       </c>
     </row>
@@ -11551,7 +11591,7 @@
       <c r="A53" s="2" t="n">
         <v>2009</v>
       </c>
-      <c r="E53" s="18" t="n">
+      <c r="E53" s="19" t="n">
         <v>0.775</v>
       </c>
     </row>
@@ -11559,7 +11599,7 @@
       <c r="A54" s="2" t="n">
         <v>2010</v>
       </c>
-      <c r="E54" s="18" t="n">
+      <c r="E54" s="19" t="n">
         <v>0.852</v>
       </c>
     </row>
@@ -11567,7 +11607,7 @@
       <c r="A55" s="2" t="n">
         <v>2011</v>
       </c>
-      <c r="E55" s="18" t="n">
+      <c r="E55" s="19" t="n">
         <v>1.034</v>
       </c>
     </row>
@@ -11575,7 +11615,7 @@
       <c r="A56" s="2" t="n">
         <v>2012</v>
       </c>
-      <c r="E56" s="18" t="n">
+      <c r="E56" s="19" t="n">
         <v>1.259</v>
       </c>
     </row>
@@ -11583,7 +11623,7 @@
       <c r="A57" s="2" t="n">
         <v>2013</v>
       </c>
-      <c r="E57" s="18" t="n">
+      <c r="E57" s="19" t="n">
         <v>1.249</v>
       </c>
     </row>
@@ -11591,7 +11631,7 @@
       <c r="A58" s="2" t="n">
         <v>2014</v>
       </c>
-      <c r="E58" s="18" t="n">
+      <c r="E58" s="19" t="n">
         <v>1.415</v>
       </c>
     </row>
@@ -11599,7 +11639,7 @@
       <c r="A59" s="2" t="n">
         <v>2015</v>
       </c>
-      <c r="E59" s="18" t="n">
+      <c r="E59" s="19" t="n">
         <v>0.979</v>
       </c>
     </row>
@@ -11607,7 +11647,7 @@
       <c r="A60" s="2" t="n">
         <v>2016</v>
       </c>
-      <c r="E60" s="18" t="n">
+      <c r="E60" s="19" t="n">
         <v>0.5600000000000001</v>
       </c>
     </row>
@@ -11671,10 +11711,10 @@
       <c r="B2" s="2" t="n">
         <v>2021.5</v>
       </c>
-      <c r="C2" s="18" t="n">
+      <c r="C2" s="19" t="n">
         <v>0.537</v>
       </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="19" t="n">
         <v>0.616</v>
       </c>
       <c r="E2" s="5">
@@ -11691,10 +11731,10 @@
       <c r="B3" s="2" t="n">
         <v>2021.75</v>
       </c>
-      <c r="C3" s="18" t="n">
+      <c r="C3" s="19" t="n">
         <v>0.5639999999999999</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="19" t="n">
         <v>0.637</v>
       </c>
       <c r="E3" s="5">
@@ -11711,10 +11751,10 @@
       <c r="B4" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="C4" s="18" t="n">
+      <c r="C4" s="19" t="n">
         <v>0.595</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="19" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" s="5">
@@ -11731,10 +11771,10 @@
       <c r="B5" s="2" t="n">
         <v>2022.25</v>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="19" t="n">
         <v>0.611</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="19" t="n">
         <v>0.655</v>
       </c>
       <c r="E5" s="5">
@@ -11751,10 +11791,10 @@
       <c r="B6" s="2" t="n">
         <v>2022.5</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="19" t="n">
         <v>0.569</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="19" t="n">
         <v>0.627</v>
       </c>
       <c r="E6" s="5">
@@ -11771,10 +11811,10 @@
       <c r="B7" s="2" t="n">
         <v>2022.75</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="19" t="n">
         <v>0.555</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="19" t="n">
         <v>0.614</v>
       </c>
       <c r="E7" s="5">
@@ -11791,10 +11831,10 @@
       <c r="B8" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>0.542</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="19" t="n">
         <v>0.592</v>
       </c>
       <c r="E8" s="5">
@@ -11811,10 +11851,10 @@
       <c r="B9" s="2" t="n">
         <v>2023.25</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="19" t="n">
         <v>0.551</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="19" t="n">
         <v>0.595</v>
       </c>
       <c r="E9" s="5">
@@ -11831,10 +11871,10 @@
       <c r="B10" s="2" t="n">
         <v>2023.5</v>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="19" t="n">
         <v>0.5620000000000001</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="19" t="n">
         <v>0.596</v>
       </c>
       <c r="E10" s="5">
@@ -11851,10 +11891,10 @@
       <c r="B11" s="2" t="n">
         <v>2023.75</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>0.63</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="19" t="n">
         <v>0.6860000000000001</v>
       </c>
       <c r="E11" s="5">
@@ -11871,10 +11911,10 @@
       <c r="B12" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>0.715</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>0.78</v>
       </c>
       <c r="E12" s="5">
@@ -11891,10 +11931,10 @@
       <c r="B13" s="2" t="n">
         <v>2024.25</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>0.829</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>0.896</v>
       </c>
       <c r="E13" s="5">
@@ -11911,10 +11951,10 @@
       <c r="B14" s="2" t="n">
         <v>2024.5</v>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>0.901</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>1.013</v>
       </c>
       <c r="E14" s="5">
@@ -11931,10 +11971,10 @@
       <c r="B15" s="2" t="n">
         <v>2024.75</v>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>1.036</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>1.147</v>
       </c>
       <c r="E15" s="5">
@@ -11951,10 +11991,10 @@
       <c r="B16" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <v>1.187</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>1.334</v>
       </c>
       <c r="E16" s="5">
@@ -11971,10 +12011,10 @@
       <c r="B17" s="2" t="n">
         <v>2025.25</v>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="19" t="n">
         <v>1.379</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="19" t="n">
         <v>1.558</v>
       </c>
       <c r="E17" s="5">
@@ -11991,10 +12031,10 @@
       <c r="B18" s="2" t="n">
         <v>2025.5</v>
       </c>
-      <c r="C18" s="18" t="n">
+      <c r="C18" s="19" t="n">
         <v>1.536</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="19" t="n">
         <v>1.702</v>
       </c>
       <c r="E18" s="5">
@@ -12016,24 +12056,492 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Fiscal quarter ends</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Oracle capex ($bn)</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Months covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2019-11-30</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2019 - Nov 2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2020-02-29</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Dec 2019 - Feb 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2020-05-31</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Mar 2020 - May 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2020 - Aug 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2020-11-30</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2020 - Nov 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2021-02-28</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Dec 2020 - Feb 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2021-05-31</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Mar 2021 - May 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2021 - Aug 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2021-11-30</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2021 - Nov 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-28</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Dec 2021 - Feb 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2022-05-31</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Mar 2022 - May 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2022 - Aug 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2022-11-30</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2022 - Nov 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2023-02-28</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>2.628</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Dec 2022 - Feb 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>1.913</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Mar 2023 - May 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2023 - Aug 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2023 - Nov 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>1.674</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Dec 2023 - Feb 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>2.798</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Mar 2024 - May 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>2.303</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2024 - Aug 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2024 - Nov 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>5.862</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Dec 2024 - Feb 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Mar 2025 - May 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>8.502000000000001</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2025 - Aug 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>12.033</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2025 - Nov 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>18.635</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Dec 2025 - Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>16.493</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Mar 2026 - May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>28.499</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026 - Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Discrete quarters from Oracle's 10-Q year-to-date cash flows (Q4 = fiscal year minus 9 months), SEC XBRL PaymentsToAcquirePropertyPlantAndEquipment. Fiscal year ends 31 May.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>TTM to</t>
+          <t>Calendar quarter</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
@@ -12058,789 +12566,1237 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>ORCL (calendarised)</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>Capex, 5 names ($bn)</t>
+          <t>Capex, 5 names</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>BEA GDP, TTM ($bn)</t>
+          <t>BEA GDP, SAAR</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>% of US GDP</t>
+          <t>TTM capex</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>TTM GDP</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>TTM capex % of GDP</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>BofA chart (PDF)</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>BofA - first-hand (pp)</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>All $bn. Blue = quarterly inputs as filed (SEC 10-Q/10-K, BEA NIPA A191RC); black = formulas.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2020Q4</t>
+          <t>2020Q1</t>
         </is>
       </c>
       <c r="B2" s="19" t="n">
-        <v>17.6</v>
+        <v>3.767</v>
       </c>
       <c r="C2" s="19" t="n">
-        <v>22.3</v>
+        <v>6.005</v>
       </c>
       <c r="D2" s="19" t="n">
-        <v>40.1</v>
+        <v>6.795</v>
       </c>
       <c r="E2" s="19" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="F2" s="19" t="n">
-        <v>1.8</v>
+        <v>3.558</v>
+      </c>
+      <c r="F2" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B3+1/3*'Oracle fiscal quarters'!B4</f>
+        <v/>
       </c>
       <c r="G2" s="8">
         <f>SUM(B2:F2)</f>
         <v/>
       </c>
       <c r="H2" s="20" t="n">
-        <v>21375</v>
-      </c>
-      <c r="I2" s="5">
-        <f>G2/H2*100</f>
-        <v/>
+        <v>21751.238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2021Q1</t>
+          <t>2020Q2</t>
         </is>
       </c>
       <c r="B3" s="19" t="n">
-        <v>18.9</v>
+        <v>4.744</v>
       </c>
       <c r="C3" s="19" t="n">
-        <v>22.2</v>
+        <v>5.391</v>
       </c>
       <c r="D3" s="19" t="n">
-        <v>45.4</v>
+        <v>7.459</v>
       </c>
       <c r="E3" s="19" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="F3" s="19" t="n">
-        <v>1.9</v>
+        <v>3.255</v>
+      </c>
+      <c r="F3" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B4+1/3*'Oracle fiscal quarters'!B5</f>
+        <v/>
       </c>
       <c r="G3" s="8">
         <f>SUM(B3:F3)</f>
         <v/>
       </c>
       <c r="H3" s="20" t="n">
-        <v>21614</v>
-      </c>
-      <c r="I3" s="5">
-        <f>G3/H3*100</f>
-        <v/>
+        <v>19958.291</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2021Q2</t>
+          <t>2020Q3</t>
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>20.6</v>
+        <v>4.907</v>
       </c>
       <c r="C4" s="19" t="n">
-        <v>22.3</v>
+        <v>5.406</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>52.3</v>
+        <v>11.063</v>
       </c>
       <c r="E4" s="19" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="F4" s="19" t="n">
-        <v>2.1</v>
+        <v>3.689</v>
+      </c>
+      <c r="F4" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B5+1/3*'Oracle fiscal quarters'!B6</f>
+        <v/>
       </c>
       <c r="G4" s="8">
         <f>SUM(B4:F4)</f>
         <v/>
       </c>
       <c r="H4" s="20" t="n">
-        <v>22488</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4*100</f>
-        <v/>
+        <v>21704.437</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2021Q3</t>
+          <t>2020Q4</t>
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>21.5</v>
+        <v>4.174</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>23.7</v>
+        <v>5.479</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>56.9</v>
+        <v>14.823</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>2.8</v>
+        <v>4.661</v>
+      </c>
+      <c r="F5" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B6+1/3*'Oracle fiscal quarters'!B7</f>
+        <v/>
       </c>
       <c r="G5" s="8">
         <f>SUM(B5:F5)</f>
         <v/>
       </c>
       <c r="H5" s="20" t="n">
-        <v>23062</v>
-      </c>
-      <c r="I5" s="5">
-        <f>G5/H5*100</f>
+        <v>22087.16</v>
+      </c>
+      <c r="I5" s="8">
+        <f>SUM(G2:G5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="21">
+        <f>AVERAGE(H2:H5)</f>
+        <v/>
+      </c>
+      <c r="K5" s="5">
+        <f>I5/J5*100</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2021Q4</t>
+          <t>2021Q1</t>
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>23.2</v>
+        <v>5.089</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>24.6</v>
+        <v>5.942</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>61.1</v>
+        <v>12.082</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>3.1</v>
+        <v>4.303</v>
+      </c>
+      <c r="F6" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B7+1/3*'Oracle fiscal quarters'!B8</f>
+        <v/>
       </c>
       <c r="G6" s="8">
         <f>SUM(B6:F6)</f>
         <v/>
       </c>
       <c r="H6" s="20" t="n">
-        <v>23746</v>
-      </c>
-      <c r="I6" s="5">
-        <f>G6/H6*100</f>
+        <v>22704.65</v>
+      </c>
+      <c r="I6" s="8">
+        <f>SUM(G3:G6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="21">
+        <f>AVERAGE(H3:H6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="5">
+        <f>I6/J6*100</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2022Q1</t>
+          <t>2021Q2</t>
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>23.5</v>
+        <v>6.452</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>28.5</v>
+        <v>5.496</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>63.9</v>
+        <v>14.288</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>3.8</v>
+        <v>4.641</v>
+      </c>
+      <c r="F7" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B8+1/3*'Oracle fiscal quarters'!B9</f>
+        <v/>
       </c>
       <c r="G7" s="8">
         <f>SUM(B7:F7)</f>
         <v/>
       </c>
       <c r="H7" s="20" t="n">
-        <v>24385</v>
-      </c>
-      <c r="I7" s="5">
-        <f>G7/H7*100</f>
+        <v>23456.708</v>
+      </c>
+      <c r="I7" s="8">
+        <f>SUM(G4:G7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="21">
+        <f>AVERAGE(H4:H7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="5">
+        <f>I7/J7*100</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2022Q2</t>
+          <t>2021Q3</t>
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>23.9</v>
+        <v>5.81</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>29.8</v>
+        <v>6.819</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>65.40000000000001</v>
+        <v>15.748</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>4.5</v>
+        <v>4.346</v>
+      </c>
+      <c r="F8" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B9+1/3*'Oracle fiscal quarters'!B10</f>
+        <v/>
       </c>
       <c r="G8" s="8">
         <f>SUM(B8:F8)</f>
         <v/>
       </c>
       <c r="H8" s="20" t="n">
-        <v>24988</v>
-      </c>
-      <c r="I8" s="5">
-        <f>G8/H8*100</f>
+        <v>23998.844</v>
+      </c>
+      <c r="I8" s="8">
+        <f>SUM(G5:G8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="21">
+        <f>AVERAGE(H5:H8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="5">
+        <f>I8/J8*100</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2022Q3</t>
+          <t>2021Q4</t>
         </is>
       </c>
       <c r="B9" s="19" t="n">
-        <v>24.4</v>
+        <v>5.865</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>30.3</v>
+        <v>6.383</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>66</v>
+        <v>18.935</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
+      </c>
+      <c r="F9" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B10+1/3*'Oracle fiscal quarters'!B11</f>
+        <v/>
       </c>
       <c r="G9" s="8">
         <f>SUM(B9:F9)</f>
         <v/>
       </c>
       <c r="H9" s="20" t="n">
-        <v>25572</v>
-      </c>
-      <c r="I9" s="5">
-        <f>G9/H9*100</f>
+        <v>24823.19</v>
+      </c>
+      <c r="I9" s="8">
+        <f>SUM(G6:G9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="21">
+        <f>AVERAGE(H6:H9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="5">
+        <f>I9/J9*100</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2022Q4</t>
+          <t>2022Q1</t>
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>24.8</v>
+        <v>5.34</v>
       </c>
       <c r="C10" s="19" t="n">
-        <v>31.5</v>
+        <v>9.786</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>63.6</v>
+        <v>14.951</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>6.7</v>
+        <v>5.441</v>
+      </c>
+      <c r="F10" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B11+1/3*'Oracle fiscal quarters'!B12</f>
+        <v/>
       </c>
       <c r="G10" s="8">
         <f>SUM(B10:F10)</f>
         <v/>
       </c>
       <c r="H10" s="20" t="n">
-        <v>26060</v>
-      </c>
-      <c r="I10" s="5">
-        <f>G10/H10*100</f>
+        <v>25259.992</v>
+      </c>
+      <c r="I10" s="8">
+        <f>SUM(G7:G10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="21">
+        <f>AVERAGE(H7:H10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="5">
+        <f>I10/J10*100</f>
+        <v/>
+      </c>
+      <c r="L10" s="19" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="M10" s="17">
+        <f>L10-K10</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2023Q1</t>
+          <t>2022Q2</t>
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>26</v>
+        <v>6.871</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>28</v>
+        <v>6.828</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>62.9</v>
+        <v>15.724</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.572</v>
+      </c>
+      <c r="F11" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B12+1/3*'Oracle fiscal quarters'!B13</f>
+        <v/>
       </c>
       <c r="G11" s="8">
         <f>SUM(B11:F11)</f>
         <v/>
       </c>
       <c r="H11" s="20" t="n">
-        <v>26555</v>
-      </c>
-      <c r="I11" s="5">
-        <f>G11/H11*100</f>
+        <v>25869.353</v>
+      </c>
+      <c r="I11" s="8">
+        <f>SUM(G8:G11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="21">
+        <f>AVERAGE(H8:H11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="5">
+        <f>I11/J11*100</f>
+        <v/>
+      </c>
+      <c r="L11" s="19" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="M11" s="17">
+        <f>L11-K11</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2023Q2</t>
+          <t>2022Q3</t>
         </is>
       </c>
       <c r="B12" s="19" t="n">
-        <v>28.1</v>
+        <v>6.283</v>
       </c>
       <c r="C12" s="19" t="n">
-        <v>28</v>
+        <v>7.276</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>58.6</v>
+        <v>16.378</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>8.699999999999999</v>
+        <v>9.375</v>
+      </c>
+      <c r="F12" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B13+1/3*'Oracle fiscal quarters'!B14</f>
+        <v/>
       </c>
       <c r="G12" s="8">
         <f>SUM(B12:F12)</f>
         <v/>
       </c>
       <c r="H12" s="20" t="n">
-        <v>26971</v>
-      </c>
-      <c r="I12" s="5">
-        <f>G12/H12*100</f>
+        <v>26335.374</v>
+      </c>
+      <c r="I12" s="8">
+        <f>SUM(G9:G12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="21">
+        <f>AVERAGE(H9:H12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="5">
+        <f>I12/J12*100</f>
+        <v/>
+      </c>
+      <c r="L12" s="19" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="M12" s="17">
+        <f>L12-K12</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2023Q3</t>
+          <t>2022Q4</t>
         </is>
       </c>
       <c r="B13" s="19" t="n">
-        <v>31.7</v>
+        <v>6.274</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>28.8</v>
+        <v>7.595</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>54.7</v>
+        <v>16.592</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>8.300000000000001</v>
+        <v>8.798</v>
+      </c>
+      <c r="F13" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B14+1/3*'Oracle fiscal quarters'!B15</f>
+        <v/>
       </c>
       <c r="G13" s="8">
         <f>SUM(B13:F13)</f>
         <v/>
       </c>
       <c r="H13" s="20" t="n">
-        <v>27403</v>
-      </c>
-      <c r="I13" s="5">
-        <f>G13/H13*100</f>
+        <v>26774.117</v>
+      </c>
+      <c r="I13" s="8">
+        <f>SUM(G10:G13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="21">
+        <f>AVERAGE(H10:H13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="5">
+        <f>I13/J13*100</f>
+        <v/>
+      </c>
+      <c r="L13" s="19" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="M13" s="17">
+        <f>L13-K13</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2023Q1</t>
         </is>
       </c>
       <c r="B14" s="19" t="n">
-        <v>35.2</v>
+        <v>6.607</v>
       </c>
       <c r="C14" s="19" t="n">
-        <v>32.3</v>
+        <v>6.289</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>52.7</v>
+        <v>14.207</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>27</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>6.9</v>
+        <v>6.823</v>
+      </c>
+      <c r="F14" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B15+1/3*'Oracle fiscal quarters'!B16</f>
+        <v/>
       </c>
       <c r="G14" s="8">
         <f>SUM(B14:F14)</f>
         <v/>
       </c>
       <c r="H14" s="20" t="n">
-        <v>27826</v>
-      </c>
-      <c r="I14" s="5">
-        <f>G14/H14*100</f>
+        <v>27241.282</v>
+      </c>
+      <c r="I14" s="8">
+        <f>SUM(G11:G14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="21">
+        <f>AVERAGE(H11:H14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="5">
+        <f>I14/J14*100</f>
+        <v/>
+      </c>
+      <c r="L14" s="19" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="M14" s="17">
+        <f>L14-K14</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2024Q1</t>
+          <t>2023Q2</t>
         </is>
       </c>
       <c r="B15" s="19" t="n">
-        <v>39.5</v>
+        <v>8.943</v>
       </c>
       <c r="C15" s="19" t="n">
-        <v>38</v>
+        <v>6.888</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>53.4</v>
+        <v>11.455</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>6</v>
+        <v>6.134</v>
+      </c>
+      <c r="F15" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B16+1/3*'Oracle fiscal quarters'!B17</f>
+        <v/>
       </c>
       <c r="G15" s="8">
         <f>SUM(B15:F15)</f>
         <v/>
       </c>
       <c r="H15" s="20" t="n">
-        <v>28214</v>
-      </c>
-      <c r="I15" s="5">
-        <f>G15/H15*100</f>
+        <v>27533.925</v>
+      </c>
+      <c r="I15" s="8">
+        <f>SUM(G12:G15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="21">
+        <f>AVERAGE(H12:H15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="5">
+        <f>I15/J15*100</f>
+        <v/>
+      </c>
+      <c r="L15" s="19" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="M15" s="17">
+        <f>L15-K15</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2024Q2</t>
+          <t>2023Q3</t>
         </is>
       </c>
       <c r="B16" s="19" t="n">
-        <v>44.5</v>
+        <v>9.917</v>
       </c>
       <c r="C16" s="19" t="n">
-        <v>44.3</v>
+        <v>8.055</v>
       </c>
       <c r="D16" s="19" t="n">
-        <v>59.6</v>
+        <v>12.479</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <v>6.9</v>
+        <v>6.496</v>
+      </c>
+      <c r="F16" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B17+1/3*'Oracle fiscal quarters'!B18</f>
+        <v/>
       </c>
       <c r="G16" s="8">
         <f>SUM(B16:F16)</f>
         <v/>
       </c>
       <c r="H16" s="20" t="n">
-        <v>28639</v>
-      </c>
-      <c r="I16" s="5">
-        <f>G16/H16*100</f>
+        <v>28064.032</v>
+      </c>
+      <c r="I16" s="8">
+        <f>SUM(G13:G16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="21">
+        <f>AVERAGE(H13:H16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="5">
+        <f>I16/J16*100</f>
+        <v/>
+      </c>
+      <c r="L16" s="19" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="M16" s="17">
+        <f>L16-K16</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2024Q3</t>
+          <t>2023Q4</t>
         </is>
       </c>
       <c r="B17" s="19" t="n">
-        <v>49.5</v>
+        <v>9.734999999999999</v>
       </c>
       <c r="C17" s="19" t="n">
-        <v>49.3</v>
+        <v>11.019</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>69.8</v>
+        <v>14.588</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>7.9</v>
+        <v>7.592</v>
+      </c>
+      <c r="F17" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B18+1/3*'Oracle fiscal quarters'!B19</f>
+        <v/>
       </c>
       <c r="G17" s="8">
         <f>SUM(B17:F17)</f>
         <v/>
       </c>
       <c r="H17" s="20" t="n">
-        <v>29015</v>
-      </c>
-      <c r="I17" s="5">
-        <f>G17/H17*100</f>
+        <v>28464.306</v>
+      </c>
+      <c r="I17" s="8">
+        <f>SUM(G14:G17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="21">
+        <f>AVERAGE(H14:H17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="5">
+        <f>I17/J17*100</f>
+        <v/>
+      </c>
+      <c r="L17" s="19" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="M17" s="17">
+        <f>L17-K17</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2024Q4</t>
+          <t>2024Q1</t>
         </is>
       </c>
       <c r="B18" s="19" t="n">
-        <v>55.6</v>
+        <v>10.952</v>
       </c>
       <c r="C18" s="19" t="n">
-        <v>52.5</v>
+        <v>12.012</v>
       </c>
       <c r="D18" s="19" t="n">
-        <v>83</v>
+        <v>14.925</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="F18" s="19" t="n">
-        <v>10.7</v>
+        <v>6.4</v>
+      </c>
+      <c r="F18" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B19+1/3*'Oracle fiscal quarters'!B20</f>
+        <v/>
       </c>
       <c r="G18" s="8">
         <f>SUM(B18:F18)</f>
         <v/>
       </c>
       <c r="H18" s="20" t="n">
-        <v>29381</v>
-      </c>
-      <c r="I18" s="5">
-        <f>G18/H18*100</f>
+        <v>28793.191</v>
+      </c>
+      <c r="I18" s="8">
+        <f>SUM(G15:G18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="21">
+        <f>AVERAGE(H15:H18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="5">
+        <f>I18/J18*100</f>
+        <v/>
+      </c>
+      <c r="L18" s="19" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="M18" s="17">
+        <f>L18-K18</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2025Q1</t>
+          <t>2024Q2</t>
         </is>
       </c>
       <c r="B19" s="19" t="n">
-        <v>61.3</v>
+        <v>13.873</v>
       </c>
       <c r="C19" s="19" t="n">
-        <v>57.7</v>
+        <v>13.186</v>
       </c>
       <c r="D19" s="19" t="n">
-        <v>93.09999999999999</v>
+        <v>17.62</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="F19" s="19" t="n">
-        <v>14.9</v>
+        <v>8.173</v>
+      </c>
+      <c r="F19" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B20+1/3*'Oracle fiscal quarters'!B21</f>
+        <v/>
       </c>
       <c r="G19" s="8">
         <f>SUM(B19:F19)</f>
         <v/>
       </c>
       <c r="H19" s="20" t="n">
-        <v>29726</v>
-      </c>
-      <c r="I19" s="5">
-        <f>G19/H19*100</f>
+        <v>29232.964</v>
+      </c>
+      <c r="I19" s="8">
+        <f>SUM(G16:G19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="21">
+        <f>AVERAGE(H16:H19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="5">
+        <f>I19/J19*100</f>
+        <v/>
+      </c>
+      <c r="L19" s="19" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M19" s="17">
+        <f>L19-K19</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2025Q2</t>
+          <t>2024Q3</t>
         </is>
       </c>
       <c r="B20" s="19" t="n">
-        <v>64.59999999999999</v>
+        <v>14.923</v>
       </c>
       <c r="C20" s="19" t="n">
-        <v>67</v>
+        <v>13.061</v>
       </c>
       <c r="D20" s="19" t="n">
-        <v>107.7</v>
+        <v>22.62</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="F20" s="19" t="n">
-        <v>21.2</v>
+        <v>8.257999999999999</v>
+      </c>
+      <c r="F20" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B21+1/3*'Oracle fiscal quarters'!B22</f>
+        <v/>
       </c>
       <c r="G20" s="8">
         <f>SUM(B20:F20)</f>
         <v/>
       </c>
       <c r="H20" s="20" t="n">
-        <v>30075</v>
-      </c>
-      <c r="I20" s="5">
-        <f>G20/H20*100</f>
+        <v>29568.256</v>
+      </c>
+      <c r="I20" s="8">
+        <f>SUM(G17:G20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="21">
+        <f>AVERAGE(H17:H20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="5">
+        <f>I20/J20*100</f>
+        <v/>
+      </c>
+      <c r="L20" s="19" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="M20" s="17">
+        <f>L20-K20</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2025Q3</t>
+          <t>2024Q4</t>
         </is>
       </c>
       <c r="B21" s="19" t="n">
-        <v>69</v>
+        <v>15.804</v>
       </c>
       <c r="C21" s="19" t="n">
-        <v>77.90000000000001</v>
+        <v>14.276</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>120.1</v>
+        <v>27.834</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="F21" s="19" t="n">
-        <v>27.4</v>
+        <v>14.425</v>
+      </c>
+      <c r="F21" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B22+1/3*'Oracle fiscal quarters'!B23</f>
+        <v/>
       </c>
       <c r="G21" s="8">
         <f>SUM(B21:F21)</f>
         <v/>
       </c>
       <c r="H21" s="20" t="n">
-        <v>30478</v>
-      </c>
-      <c r="I21" s="5">
-        <f>G21/H21*100</f>
+        <v>29929.552</v>
+      </c>
+      <c r="I21" s="8">
+        <f>SUM(G18:G21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="21">
+        <f>AVERAGE(H18:H21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="5">
+        <f>I21/J21*100</f>
+        <v/>
+      </c>
+      <c r="L21" s="19" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="M21" s="17">
+        <f>L21-K21</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2025Q1</t>
         </is>
       </c>
       <c r="B22" s="19" t="n">
-        <v>83.09999999999999</v>
+        <v>16.745</v>
       </c>
       <c r="C22" s="19" t="n">
-        <v>91.40000000000001</v>
+        <v>17.197</v>
       </c>
       <c r="D22" s="19" t="n">
-        <v>131.8</v>
+        <v>25.019</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="F22" s="19" t="n">
-        <v>35.5</v>
+        <v>12.941</v>
+      </c>
+      <c r="F22" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B23+1/3*'Oracle fiscal quarters'!B24</f>
+        <v/>
       </c>
       <c r="G22" s="8">
         <f>SUM(B22:F22)</f>
         <v/>
       </c>
       <c r="H22" s="20" t="n">
-        <v>30861</v>
-      </c>
-      <c r="I22" s="5">
-        <f>G22/H22*100</f>
+        <v>30171.979</v>
+      </c>
+      <c r="I22" s="8">
+        <f>SUM(G19:G22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="21">
+        <f>AVERAGE(H19:H22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="5">
+        <f>I22/J22*100</f>
+        <v/>
+      </c>
+      <c r="L22" s="19" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="M22" s="17">
+        <f>L22-K22</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2025Q2</t>
         </is>
       </c>
       <c r="B23" s="19" t="n">
-        <v>97.2</v>
+        <v>17.079</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>109.9</v>
+        <v>22.446</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>151</v>
+        <v>32.183</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="F23" s="19" t="n">
-        <v>48.2</v>
+        <v>16.538</v>
+      </c>
+      <c r="F23" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B24+1/3*'Oracle fiscal quarters'!B25</f>
+        <v/>
       </c>
       <c r="G23" s="8">
         <f>SUM(B23:F23)</f>
         <v/>
       </c>
       <c r="H23" s="20" t="n">
-        <v>31295</v>
-      </c>
-      <c r="I23" s="5">
-        <f>G23/H23*100</f>
+        <v>30630.174</v>
+      </c>
+      <c r="I23" s="8">
+        <f>SUM(G20:G23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="21">
+        <f>AVERAGE(H20:H23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="5">
+        <f>I23/J23*100</f>
+        <v/>
+      </c>
+      <c r="L23" s="19" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="M23" s="17">
+        <f>L23-K23</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2025Q3</t>
         </is>
       </c>
       <c r="B24" s="19" t="n">
-        <v>115.9</v>
+        <v>19.394</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>132.4</v>
+        <v>23.953</v>
       </c>
       <c r="D24" s="19" t="n">
-        <v>173</v>
+        <v>35.095</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="F24" s="19" t="n">
-        <v>55.7</v>
+        <v>18.829</v>
+      </c>
+      <c r="F24" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B25+1/3*'Oracle fiscal quarters'!B26</f>
+        <v/>
       </c>
       <c r="G24" s="8">
         <f>SUM(B24:F24)</f>
         <v/>
       </c>
       <c r="H24" s="20" t="n">
-        <v>31778</v>
-      </c>
-      <c r="I24" s="5">
-        <f>G24/H24*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25"/>
+        <v>31180.493</v>
+      </c>
+      <c r="I24" s="8">
+        <f>SUM(G21:G24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="21">
+        <f>AVERAGE(H21:H24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="5">
+        <f>I24/J24*100</f>
+        <v/>
+      </c>
+      <c r="L24" s="19" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="M24" s="17">
+        <f>L24-K24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>29.876</v>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>27.851</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>39.522</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>21.383</v>
+      </c>
+      <c r="F25" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B26+1/3*'Oracle fiscal quarters'!B27</f>
+        <v/>
+      </c>
+      <c r="G25" s="8">
+        <f>SUM(B25:F25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>31462.523</v>
+      </c>
+      <c r="I25" s="8">
+        <f>SUM(G22:G25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="21">
+        <f>AVERAGE(H22:H25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="5">
+        <f>I25/J25*100</f>
+        <v/>
+      </c>
+      <c r="L25" s="19" t="n">
+        <v>1.379</v>
+      </c>
+      <c r="M25" s="17">
+        <f>L25-K25</f>
+        <v/>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SEC XBRL purchases of property &amp; equipment (Amazon: PaymentsToAcquireProductiveAssets), discrete quarters from YTD filings; Oracle's Aug/Nov/Feb/May quarters go in the calendar quarter they end in; GDP = BEA NIPA A191RC. Runs past the exhibit's last point (TTM to 2026Q1).</t>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>30.876</v>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>35.674</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>44.203</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>18.997</v>
+      </c>
+      <c r="F26" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B27+1/3*'Oracle fiscal quarters'!B28</f>
+        <v/>
+      </c>
+      <c r="G26" s="8">
+        <f>SUM(B26:F26)</f>
+        <v/>
+      </c>
+      <c r="H26" s="20" t="n">
+        <v>31906.274</v>
+      </c>
+      <c r="I26" s="8">
+        <f>SUM(G23:G26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="21">
+        <f>AVERAGE(H23:H26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="5">
+        <f>I26/J26*100</f>
+        <v/>
+      </c>
+      <c r="L26" s="19" t="n">
+        <v>1.536</v>
+      </c>
+      <c r="M26" s="17">
+        <f>L26-K26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>35.802</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>44.924</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>54.208</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>30.116</v>
+      </c>
+      <c r="F27" s="5">
+        <f>2/3*'Oracle fiscal quarters'!B28+1/3*'Oracle fiscal quarters'!B29</f>
+        <v/>
+      </c>
+      <c r="G27" s="8">
+        <f>SUM(B27:F27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="20" t="n">
+        <v>32563.03</v>
+      </c>
+      <c r="I27" s="8">
+        <f>SUM(G24:G27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="21">
+        <f>AVERAGE(H24:H27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="5">
+        <f>I27/J27*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Oracle's fiscal quarters end Feb/May/Aug/Nov; each calendar quarter = 2/3 x the Oracle quarter ending in its second month + 1/3 x the next Oracle quarter (Oracle fiscal quarters sheet). The others end on calendar quarter ends (Microsoft's June fiscal year included). Discrete quarters come from year-to-date cash flows (Q4 = year minus 9 months).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>BofA's chart plots each point three quarters early: its last point (drawn at mid-2025) is the TTM to 2026Q1.</t>
         </is>
       </c>
     </row>
@@ -12852,7 +13808,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/bofa-capex-cycles/20261015_BofA Exhibit 2 - capex cycles (% of GDP).xlsx
+++ b/bofa-capex-cycles/20261015_BofA Exhibit 2 - capex cycles (% of GDP).xlsx
@@ -976,6 +976,392 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>First-hand hyperscaler capex, TTM, % of US GDP</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Five hyperscalers (MSFT, GOOGL, AMZN, META, ORCL)</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Hyperscalers first-hand'!$A$5:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Hyperscalers first-hand'!$K$5:$K$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Five + CoreWeave + SpaceX AI (where reported periods allow)</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="8A5CD6"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8A5CD6"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8A5CD6"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Hyperscalers first-hand'!$A$5:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Hyperscalers first-hand'!$R$5:$R$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0">
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="4"/>
+        <tickMarkSkip val="4"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="0.0&quot;%&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0">
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0">
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>First-hand hyperscaler capex, TTM, $bn</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Five hyperscalers (MSFT, GOOGL, AMZN, META, ORCL)</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Hyperscalers first-hand'!$A$5:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Hyperscalers first-hand'!$I$5:$I$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Five + CoreWeave + SpaceX AI (where reported periods allow)</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="8A5CD6"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8A5CD6"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8A5CD6"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Hyperscalers first-hand'!$A$5:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Hyperscalers first-hand'!$Q$5:$Q$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0">
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="4"/>
+        <tickMarkSkip val="4"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0">
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0">
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1039,6 +1425,55 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3420000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3420000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -13953,8 +14388,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/bofa-capex-cycles/20261015_BofA Exhibit 2 - capex cycles (% of GDP).xlsx
+++ b/bofa-capex-cycles/20261015_BofA Exhibit 2 - capex cycles (% of GDP).xlsx
@@ -15032,18 +15032,18 @@
         <v>1</v>
       </c>
       <c r="H66" s="13">
-        <f t="shared" ref="H66:H97" si="6">C66*G66/E66*100</f>
+        <f t="shared" ref="H66:H79" si="6">C66*G66/E66*100</f>
         <v>0.60733985939750912</v>
       </c>
       <c r="I66" s="16">
         <v>0.61099999999999999</v>
       </c>
       <c r="J66" s="17">
-        <f t="shared" ref="J66:J97" si="7">I66-H66</f>
+        <f t="shared" ref="J66:J79" si="7">I66-H66</f>
         <v>3.6601406024908689E-3</v>
       </c>
       <c r="K66" s="13">
-        <f t="shared" ref="K66:K97" si="8">ABS(J66)</f>
+        <f t="shared" ref="K66:K79" si="8">ABS(J66)</f>
         <v>3.6601406024908689E-3</v>
       </c>
       <c r="L66" s="2" t="s">
